--- a/public/assets/templates/maintenance/utility.xlsx
+++ b/public/assets/templates/maintenance/utility.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkPad\Documents\MAGANG\PT BAS\ENG\Maintenance\Template Laporan Form\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC3EADDF-373A-4B5A-B2A8-0FA763849176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B7E1CB7-2EE5-41A1-9FC1-1F3C45838383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{FF133B37-4395-463D-9E0A-8A8115D83F24}"/>
   </bookViews>
@@ -753,246 +753,252 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1376,924 +1382,924 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickTop="1">
-      <c r="A1" s="79"/>
-      <c r="B1" s="78"/>
-      <c r="C1" s="77" t="s">
+      <c r="A1" s="55"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="76"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="75"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="73" t="s">
+      <c r="A2" s="57"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="72"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="10" customHeight="1">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="70" t="s">
+      <c r="B3" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="70"/>
-      <c r="D3" s="69" t="s">
+      <c r="C3" s="18"/>
+      <c r="D3" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E3" s="69"/>
-      <c r="F3" s="68" t="s">
+      <c r="E3" s="24"/>
+      <c r="F3" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="68"/>
-      <c r="H3" s="67"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="26"/>
     </row>
     <row r="4" spans="1:8" ht="10" customHeight="1">
-      <c r="A4" s="71" t="s">
+      <c r="A4" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="70"/>
-      <c r="D4" s="69" t="s">
+      <c r="C4" s="18"/>
+      <c r="D4" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="69"/>
-      <c r="F4" s="68" t="s">
+      <c r="E4" s="24"/>
+      <c r="F4" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="68"/>
-      <c r="H4" s="67"/>
-    </row>
-    <row r="5" spans="1:8" s="60" customFormat="1" ht="11" customHeight="1">
-      <c r="A5" s="66" t="s">
+      <c r="G4" s="25"/>
+      <c r="H4" s="26"/>
+    </row>
+    <row r="5" spans="1:8" s="15" customFormat="1" ht="11" customHeight="1">
+      <c r="A5" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="65" t="s">
+      <c r="B5" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="65"/>
-      <c r="D5" s="64" t="s">
+      <c r="C5" s="30"/>
+      <c r="D5" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="63" t="s">
+      <c r="E5" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="61"/>
-    </row>
-    <row r="6" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A6" s="59" t="s">
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="33"/>
+    </row>
+    <row r="6" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A6" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="55" t="s">
+      <c r="B6" s="10"/>
+      <c r="C6" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="49"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="35"/>
-    </row>
-    <row r="7" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A7" s="59"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="55" t="s">
+      <c r="D6" s="78"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="29"/>
+    </row>
+    <row r="7" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A7" s="44"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="49"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="35"/>
-    </row>
-    <row r="8" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A8" s="59"/>
-      <c r="B8" s="49"/>
-      <c r="C8" s="55" t="s">
+      <c r="D7" s="78"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="29"/>
+    </row>
+    <row r="8" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A8" s="44"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="49"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="35"/>
-    </row>
-    <row r="9" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A9" s="59"/>
-      <c r="B9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="35"/>
-    </row>
-    <row r="10" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A10" s="57" t="s">
+      <c r="D8" s="78"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
+    </row>
+    <row r="9" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A9" s="44"/>
+      <c r="B9" s="10"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="29"/>
+    </row>
+    <row r="10" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A10" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="55" t="s">
+      <c r="B10" s="10"/>
+      <c r="C10" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="49"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="35"/>
-    </row>
-    <row r="11" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A11" s="57"/>
-      <c r="B11" s="49"/>
-      <c r="C11" s="55" t="s">
+      <c r="D10" s="78"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
+    </row>
+    <row r="11" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A11" s="45"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="49"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="35"/>
-    </row>
-    <row r="12" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A12" s="57"/>
-      <c r="B12" s="49"/>
-      <c r="C12" s="55" t="s">
+      <c r="D11" s="78"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="29"/>
+    </row>
+    <row r="12" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A12" s="45"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="49"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="35"/>
-    </row>
-    <row r="13" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A13" s="57"/>
-      <c r="B13" s="49"/>
-      <c r="C13" s="55" t="s">
+      <c r="D12" s="78"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="29"/>
+    </row>
+    <row r="13" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A13" s="45"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="49"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="35"/>
-    </row>
-    <row r="14" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A14" s="57"/>
-      <c r="B14" s="49"/>
-      <c r="C14" s="55" t="s">
+      <c r="D13" s="78"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="29"/>
+    </row>
+    <row r="14" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A14" s="45"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="49"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="35"/>
-    </row>
-    <row r="15" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A15" s="57"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="55" t="s">
+      <c r="D14" s="78"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="29"/>
+    </row>
+    <row r="15" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A15" s="45"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="49"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="35"/>
-    </row>
-    <row r="16" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A16" s="57"/>
-      <c r="B16" s="49"/>
-      <c r="C16" s="55" t="s">
+      <c r="D15" s="78"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
+    </row>
+    <row r="16" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A16" s="45"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="49"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="35"/>
-    </row>
-    <row r="17" spans="1:10" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A17" s="57"/>
-      <c r="B17" s="49"/>
-      <c r="C17" s="55" t="s">
+      <c r="D16" s="78"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="29"/>
+    </row>
+    <row r="17" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A17" s="45"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="49"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="35"/>
-      <c r="J17" s="43" t="s">
+      <c r="D17" s="78"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="29"/>
+      <c r="J17" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:10" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A18" s="57"/>
-      <c r="B18" s="49"/>
-      <c r="C18" s="55" t="s">
+    <row r="18" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A18" s="45"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="49"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="35"/>
-    </row>
-    <row r="19" spans="1:10" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A19" s="57"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="58" t="s">
+      <c r="D18" s="78"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="29"/>
+    </row>
+    <row r="19" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A19" s="45"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="49"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="35"/>
-    </row>
-    <row r="20" spans="1:10" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A20" s="57"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="58" t="s">
+      <c r="D19" s="78"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="29"/>
+    </row>
+    <row r="20" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A20" s="45"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="49"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="35"/>
-    </row>
-    <row r="21" spans="1:10" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A21" s="57"/>
-      <c r="B21" s="49"/>
-      <c r="D21" s="49"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="35"/>
-    </row>
-    <row r="22" spans="1:10" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A22" s="53" t="s">
+      <c r="D20" s="78"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="29"/>
+    </row>
+    <row r="21" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A21" s="45"/>
+      <c r="B21" s="10"/>
+      <c r="D21" s="78"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="29"/>
+    </row>
+    <row r="22" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A22" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="49"/>
-      <c r="C22" s="55" t="s">
+      <c r="B22" s="10"/>
+      <c r="C22" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="49"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="35"/>
-      <c r="J22" s="56"/>
-    </row>
-    <row r="23" spans="1:10" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A23" s="53"/>
-      <c r="B23" s="49"/>
-      <c r="C23" s="55" t="s">
+      <c r="D22" s="78"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="29"/>
+      <c r="J22" s="13"/>
+    </row>
+    <row r="23" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A23" s="46"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D23" s="49"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="35"/>
-    </row>
-    <row r="24" spans="1:10" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A24" s="53"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="55" t="s">
+      <c r="D23" s="78"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="29"/>
+    </row>
+    <row r="24" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A24" s="46"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="49"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="35"/>
-    </row>
-    <row r="25" spans="1:10" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A25" s="53"/>
-      <c r="B25" s="49"/>
-      <c r="C25" s="55" t="s">
+      <c r="D24" s="78"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="29"/>
+    </row>
+    <row r="25" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A25" s="46"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="49"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="35"/>
-    </row>
-    <row r="26" spans="1:10" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A26" s="53"/>
-      <c r="B26" s="49"/>
-      <c r="C26" s="55" t="s">
+      <c r="D25" s="78"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="29"/>
+    </row>
+    <row r="26" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A26" s="46"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="49"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="35"/>
-    </row>
-    <row r="27" spans="1:10" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A27" s="53"/>
-      <c r="B27" s="49"/>
-      <c r="C27" s="55" t="s">
+      <c r="D26" s="78"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="29"/>
+    </row>
+    <row r="27" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A27" s="46"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="49"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="35"/>
-    </row>
-    <row r="28" spans="1:10" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A28" s="53"/>
-      <c r="B28" s="49"/>
-      <c r="C28" s="55" t="s">
+      <c r="D27" s="78"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="29"/>
+    </row>
+    <row r="28" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A28" s="46"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D28" s="49"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="36"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="35"/>
-    </row>
-    <row r="29" spans="1:10" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A29" s="53"/>
-      <c r="B29" s="49"/>
-      <c r="C29" s="55" t="s">
+      <c r="D28" s="78"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="29"/>
+    </row>
+    <row r="29" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A29" s="46"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D29" s="49"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="35"/>
-    </row>
-    <row r="30" spans="1:10" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A30" s="53"/>
-      <c r="B30" s="49"/>
-      <c r="C30" s="55" t="s">
+      <c r="D29" s="78"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="29"/>
+    </row>
+    <row r="30" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A30" s="46"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D30" s="49"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="35"/>
-    </row>
-    <row r="31" spans="1:10" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A31" s="53" t="s">
+      <c r="D30" s="78"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="29"/>
+    </row>
+    <row r="31" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A31" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="49"/>
-      <c r="C31" s="54" t="s">
+      <c r="B31" s="10"/>
+      <c r="C31" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D31" s="49"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="35"/>
-    </row>
-    <row r="32" spans="1:10" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A32" s="53"/>
-      <c r="B32" s="49"/>
-      <c r="C32" s="54" t="s">
+      <c r="D31" s="78"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="29"/>
+    </row>
+    <row r="32" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A32" s="46"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="49"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="35"/>
-    </row>
-    <row r="33" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A33" s="53"/>
-      <c r="B33" s="45"/>
-      <c r="C33" s="54" t="s">
+      <c r="D32" s="78"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="29"/>
+    </row>
+    <row r="33" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A33" s="46"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="45"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="35"/>
-    </row>
-    <row r="34" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A34" s="53"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="54" t="s">
+      <c r="D33" s="79"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="29"/>
+    </row>
+    <row r="34" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A34" s="46"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="45"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="35"/>
-    </row>
-    <row r="35" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A35" s="53"/>
-      <c r="B35" s="45"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="35"/>
-    </row>
-    <row r="36" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A36" s="52" t="s">
+      <c r="D34" s="79"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="29"/>
+    </row>
+    <row r="35" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A35" s="46"/>
+      <c r="B35" s="8"/>
+      <c r="D35" s="79"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="29"/>
+    </row>
+    <row r="36" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A36" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="B36" s="49"/>
-      <c r="C36" s="48" t="s">
+      <c r="B36" s="10"/>
+      <c r="C36" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D36" s="49"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="35"/>
-    </row>
-    <row r="37" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A37" s="51"/>
-      <c r="B37" s="49"/>
-      <c r="C37" s="48" t="s">
+      <c r="D36" s="78"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="29"/>
+    </row>
+    <row r="37" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A37" s="48"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D37" s="49"/>
-      <c r="E37" s="47"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="35"/>
-    </row>
-    <row r="38" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A38" s="51"/>
-      <c r="B38" s="49"/>
-      <c r="C38" s="48" t="s">
+      <c r="D37" s="78"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="29"/>
+    </row>
+    <row r="38" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A38" s="48"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D38" s="49"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="35"/>
-    </row>
-    <row r="39" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A39" s="51"/>
-      <c r="B39" s="49"/>
-      <c r="C39" s="48" t="s">
+      <c r="D38" s="78"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="29"/>
+    </row>
+    <row r="39" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A39" s="48"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D39" s="49"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="35"/>
-    </row>
-    <row r="40" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A40" s="51"/>
-      <c r="B40" s="49"/>
-      <c r="C40" s="48" t="s">
+      <c r="D39" s="78"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="29"/>
+    </row>
+    <row r="40" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A40" s="48"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D40" s="49"/>
-      <c r="E40" s="47"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="35"/>
-    </row>
-    <row r="41" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A41" s="51"/>
-      <c r="B41" s="49"/>
-      <c r="C41" s="48" t="s">
+      <c r="D40" s="78"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="29"/>
+    </row>
+    <row r="41" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A41" s="48"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D41" s="49"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="35"/>
-    </row>
-    <row r="42" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A42" s="51"/>
-      <c r="B42" s="49"/>
-      <c r="C42" s="48" t="s">
+      <c r="D41" s="78"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="29"/>
+    </row>
+    <row r="42" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A42" s="48"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D42" s="49"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="35"/>
-    </row>
-    <row r="43" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A43" s="51"/>
-      <c r="B43" s="49"/>
-      <c r="C43" s="48" t="s">
+      <c r="D42" s="78"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="29"/>
+    </row>
+    <row r="43" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A43" s="48"/>
+      <c r="B43" s="10"/>
+      <c r="C43" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D43" s="49"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="36"/>
-      <c r="G43" s="36"/>
-      <c r="H43" s="35"/>
-    </row>
-    <row r="44" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A44" s="51"/>
-      <c r="B44" s="49"/>
-      <c r="C44" s="48" t="s">
+      <c r="D43" s="78"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="29"/>
+    </row>
+    <row r="44" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A44" s="48"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D44" s="49"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="36"/>
-      <c r="H44" s="35"/>
-    </row>
-    <row r="45" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A45" s="51"/>
-      <c r="B45" s="49"/>
-      <c r="C45" s="48" t="s">
+      <c r="D44" s="78"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="29"/>
+    </row>
+    <row r="45" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A45" s="48"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D45" s="49"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="36"/>
-      <c r="G45" s="36"/>
-      <c r="H45" s="35"/>
-    </row>
-    <row r="46" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A46" s="51"/>
-      <c r="B46" s="49"/>
-      <c r="C46" s="48" t="s">
+      <c r="D45" s="78"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="29"/>
+    </row>
+    <row r="46" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A46" s="48"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D46" s="49"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="35"/>
-    </row>
-    <row r="47" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A47" s="51"/>
-      <c r="B47" s="49"/>
-      <c r="C47" s="48" t="s">
+      <c r="D46" s="78"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="29"/>
+    </row>
+    <row r="47" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A47" s="48"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D47" s="49"/>
-      <c r="E47" s="47"/>
-      <c r="F47" s="36"/>
-      <c r="G47" s="36"/>
-      <c r="H47" s="35"/>
-    </row>
-    <row r="48" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A48" s="51"/>
-      <c r="B48" s="49"/>
-      <c r="C48" s="48" t="s">
+      <c r="D47" s="78"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="29"/>
+    </row>
+    <row r="48" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A48" s="48"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D48" s="49"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="36"/>
-      <c r="G48" s="36"/>
-      <c r="H48" s="35"/>
-    </row>
-    <row r="49" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A49" s="51"/>
-      <c r="B49" s="49"/>
-      <c r="C49" s="48" t="s">
+      <c r="D48" s="78"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="29"/>
+    </row>
+    <row r="49" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A49" s="48"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D49" s="49"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="36"/>
-      <c r="G49" s="36"/>
-      <c r="H49" s="35"/>
-    </row>
-    <row r="50" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A50" s="51"/>
-      <c r="B50" s="49"/>
-      <c r="C50" s="48" t="s">
+      <c r="D49" s="78"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="29"/>
+    </row>
+    <row r="50" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A50" s="48"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D50" s="49"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="36"/>
-      <c r="G50" s="36"/>
-      <c r="H50" s="35"/>
-    </row>
-    <row r="51" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A51" s="51"/>
-      <c r="B51" s="49"/>
-      <c r="C51" s="48" t="s">
+      <c r="D50" s="78"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="28"/>
+      <c r="H50" s="29"/>
+    </row>
+    <row r="51" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A51" s="48"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D51" s="49"/>
-      <c r="E51" s="47"/>
-      <c r="F51" s="36"/>
-      <c r="G51" s="36"/>
-      <c r="H51" s="35"/>
-    </row>
-    <row r="52" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A52" s="50"/>
-      <c r="B52" s="49"/>
-      <c r="D52" s="49"/>
-      <c r="E52" s="47"/>
-      <c r="F52" s="36"/>
-      <c r="G52" s="36"/>
-      <c r="H52" s="35"/>
-    </row>
-    <row r="53" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A53" s="46" t="s">
+      <c r="D51" s="78"/>
+      <c r="E51" s="27"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="29"/>
+    </row>
+    <row r="52" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A52" s="49"/>
+      <c r="B52" s="10"/>
+      <c r="D52" s="78"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="29"/>
+    </row>
+    <row r="53" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A53" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="B53" s="49"/>
-      <c r="C53" s="48" t="s">
+      <c r="B53" s="10"/>
+      <c r="C53" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D53" s="49"/>
-      <c r="E53" s="47"/>
-      <c r="F53" s="36"/>
-      <c r="G53" s="36"/>
-      <c r="H53" s="35"/>
-    </row>
-    <row r="54" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A54" s="46"/>
-      <c r="B54" s="45"/>
-      <c r="C54" s="48" t="s">
+      <c r="D53" s="78"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="28"/>
+      <c r="H53" s="29"/>
+    </row>
+    <row r="54" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A54" s="50"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D54" s="45"/>
-      <c r="E54" s="47"/>
-      <c r="F54" s="36"/>
-      <c r="G54" s="36"/>
-      <c r="H54" s="35"/>
-    </row>
-    <row r="55" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A55" s="46"/>
-      <c r="B55" s="45"/>
-      <c r="C55" s="48" t="s">
+      <c r="D54" s="79"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="28"/>
+      <c r="H54" s="29"/>
+    </row>
+    <row r="55" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A55" s="50"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D55" s="45"/>
-      <c r="E55" s="47"/>
-      <c r="F55" s="36"/>
-      <c r="G55" s="36"/>
-      <c r="H55" s="35"/>
-    </row>
-    <row r="56" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A56" s="46"/>
-      <c r="B56" s="45"/>
-      <c r="C56" s="48" t="s">
+      <c r="D55" s="79"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="29"/>
+    </row>
+    <row r="56" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A56" s="50"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D56" s="45"/>
-      <c r="E56" s="47"/>
-      <c r="F56" s="36"/>
-      <c r="G56" s="36"/>
-      <c r="H56" s="35"/>
-    </row>
-    <row r="57" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A57" s="46"/>
-      <c r="B57" s="45"/>
-      <c r="D57" s="45"/>
-      <c r="E57" s="36"/>
-      <c r="F57" s="36"/>
-      <c r="G57" s="36"/>
-      <c r="H57" s="35"/>
-    </row>
-    <row r="58" spans="1:8" s="43" customFormat="1" ht="9" customHeight="1">
-      <c r="A58" s="41"/>
-      <c r="B58" s="44"/>
-      <c r="C58" s="44"/>
-      <c r="D58" s="42"/>
-      <c r="E58" s="36"/>
-      <c r="F58" s="36"/>
-      <c r="G58" s="36"/>
-      <c r="H58" s="35"/>
+      <c r="D56" s="79"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="28"/>
+      <c r="G56" s="28"/>
+      <c r="H56" s="29"/>
+    </row>
+    <row r="57" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A57" s="50"/>
+      <c r="B57" s="8"/>
+      <c r="D57" s="79"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="29"/>
+    </row>
+    <row r="58" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A58" s="51"/>
+      <c r="B58" s="7"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="80"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="28"/>
+      <c r="H58" s="29"/>
     </row>
     <row r="59" spans="1:8" ht="9" customHeight="1">
-      <c r="A59" s="41"/>
-      <c r="B59" s="40"/>
-      <c r="C59" s="40"/>
-      <c r="D59" s="42"/>
-      <c r="E59" s="36"/>
-      <c r="F59" s="36"/>
-      <c r="G59" s="36"/>
-      <c r="H59" s="35"/>
+      <c r="A59" s="51"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="80"/>
+      <c r="E59" s="28"/>
+      <c r="F59" s="28"/>
+      <c r="G59" s="28"/>
+      <c r="H59" s="29"/>
     </row>
     <row r="60" spans="1:8" ht="9" customHeight="1">
-      <c r="A60" s="41"/>
-      <c r="B60" s="40"/>
-      <c r="C60" s="40"/>
-      <c r="D60" s="42"/>
-      <c r="E60" s="36"/>
-      <c r="F60" s="36"/>
-      <c r="G60" s="36"/>
-      <c r="H60" s="35"/>
+      <c r="A60" s="51"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="80"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28"/>
+      <c r="G60" s="28"/>
+      <c r="H60" s="29"/>
     </row>
     <row r="61" spans="1:8" ht="9" customHeight="1">
-      <c r="A61" s="41"/>
-      <c r="B61" s="40"/>
-      <c r="C61" s="40"/>
-      <c r="D61" s="37"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-      <c r="G61" s="36"/>
-      <c r="H61" s="35"/>
+      <c r="A61" s="51"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="81"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="29"/>
     </row>
     <row r="62" spans="1:8" ht="9" customHeight="1">
-      <c r="A62" s="41"/>
-      <c r="B62" s="40"/>
-      <c r="C62" s="40"/>
-      <c r="D62" s="37"/>
-      <c r="E62" s="36"/>
-      <c r="F62" s="36"/>
-      <c r="G62" s="36"/>
-      <c r="H62" s="35"/>
+      <c r="A62" s="51"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="81"/>
+      <c r="E62" s="28"/>
+      <c r="F62" s="28"/>
+      <c r="G62" s="28"/>
+      <c r="H62" s="29"/>
     </row>
     <row r="63" spans="1:8" ht="9" customHeight="1">
-      <c r="A63" s="41"/>
-      <c r="B63" s="40"/>
-      <c r="C63" s="40"/>
-      <c r="D63" s="37"/>
-      <c r="E63" s="36"/>
-      <c r="F63" s="36"/>
-      <c r="G63" s="36"/>
-      <c r="H63" s="35"/>
+      <c r="A63" s="51"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="81"/>
+      <c r="E63" s="28"/>
+      <c r="F63" s="28"/>
+      <c r="G63" s="28"/>
+      <c r="H63" s="29"/>
     </row>
     <row r="64" spans="1:8" ht="9" customHeight="1">
-      <c r="A64" s="39"/>
-      <c r="B64" s="38"/>
-      <c r="C64" s="38"/>
-      <c r="D64" s="37"/>
-      <c r="E64" s="36"/>
-      <c r="F64" s="36"/>
-      <c r="G64" s="36"/>
-      <c r="H64" s="35"/>
+      <c r="A64" s="52"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="81"/>
+      <c r="E64" s="28"/>
+      <c r="F64" s="28"/>
+      <c r="G64" s="28"/>
+      <c r="H64" s="29"/>
     </row>
     <row r="65" spans="1:8" ht="9" customHeight="1">
-      <c r="A65" s="15" t="s">
+      <c r="A65" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="33" t="s">
+      <c r="B65" s="66"/>
+      <c r="C65" s="66"/>
+      <c r="D65" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="E65" s="33"/>
-      <c r="F65" s="33"/>
-      <c r="G65" s="33"/>
-      <c r="H65" s="34"/>
+      <c r="E65" s="37"/>
+      <c r="F65" s="37"/>
+      <c r="G65" s="37"/>
+      <c r="H65" s="38"/>
     </row>
     <row r="66" spans="1:8" ht="9" customHeight="1">
-      <c r="A66" s="15"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="33" t="s">
+      <c r="A66" s="65"/>
+      <c r="B66" s="66"/>
+      <c r="C66" s="66"/>
+      <c r="D66" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="E66" s="33"/>
-      <c r="F66" s="33"/>
-      <c r="G66" s="32"/>
-      <c r="H66" s="31" t="s">
+      <c r="E66" s="37"/>
+      <c r="F66" s="37"/>
+      <c r="G66" s="39"/>
+      <c r="H66" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="9" customHeight="1">
-      <c r="A67" s="15"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="30"/>
-      <c r="E67" s="29"/>
-      <c r="F67" s="29"/>
-      <c r="G67" s="26"/>
-      <c r="H67" s="25"/>
+      <c r="A67" s="65"/>
+      <c r="B67" s="66"/>
+      <c r="C67" s="66"/>
+      <c r="D67" s="40"/>
+      <c r="E67" s="41"/>
+      <c r="F67" s="41"/>
+      <c r="G67" s="42"/>
+      <c r="H67" s="2"/>
     </row>
     <row r="68" spans="1:8" ht="9" customHeight="1">
-      <c r="A68" s="15"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="30"/>
-      <c r="E68" s="29"/>
-      <c r="F68" s="29"/>
-      <c r="G68" s="26"/>
-      <c r="H68" s="25"/>
+      <c r="A68" s="65"/>
+      <c r="B68" s="66"/>
+      <c r="C68" s="66"/>
+      <c r="D68" s="40"/>
+      <c r="E68" s="41"/>
+      <c r="F68" s="41"/>
+      <c r="G68" s="42"/>
+      <c r="H68" s="2"/>
     </row>
     <row r="69" spans="1:8" ht="9" customHeight="1">
-      <c r="A69" s="15"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="30"/>
-      <c r="E69" s="29"/>
-      <c r="F69" s="29"/>
-      <c r="G69" s="26"/>
-      <c r="H69" s="25"/>
+      <c r="A69" s="65"/>
+      <c r="B69" s="66"/>
+      <c r="C69" s="66"/>
+      <c r="D69" s="40"/>
+      <c r="E69" s="41"/>
+      <c r="F69" s="41"/>
+      <c r="G69" s="42"/>
+      <c r="H69" s="2"/>
     </row>
     <row r="70" spans="1:8" ht="9" customHeight="1">
-      <c r="A70" s="15"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="27"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="26"/>
-      <c r="H70" s="25"/>
+      <c r="A70" s="65"/>
+      <c r="B70" s="66"/>
+      <c r="C70" s="66"/>
+      <c r="D70" s="53"/>
+      <c r="E70" s="54"/>
+      <c r="F70" s="54"/>
+      <c r="G70" s="42"/>
+      <c r="H70" s="2"/>
     </row>
     <row r="71" spans="1:8" ht="9" customHeight="1">
-      <c r="A71" s="15"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="24" t="s">
+      <c r="A71" s="65"/>
+      <c r="B71" s="66"/>
+      <c r="C71" s="66"/>
+      <c r="D71" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="E71" s="23"/>
-      <c r="F71" s="22"/>
-      <c r="G71" s="11"/>
-      <c r="H71" s="10"/>
+      <c r="E71" s="76"/>
+      <c r="F71" s="77"/>
+      <c r="G71" s="59"/>
+      <c r="H71" s="60"/>
     </row>
     <row r="72" spans="1:8" ht="9" customHeight="1">
-      <c r="A72" s="15"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="20" t="s">
+      <c r="A72" s="65"/>
+      <c r="B72" s="66"/>
+      <c r="C72" s="66"/>
+      <c r="D72" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="E72" s="19"/>
-      <c r="F72" s="18"/>
-      <c r="G72" s="17"/>
-      <c r="H72" s="16"/>
+      <c r="E72" s="70"/>
+      <c r="F72" s="71"/>
+      <c r="G72" s="61"/>
+      <c r="H72" s="62"/>
     </row>
     <row r="73" spans="1:8" ht="9" customHeight="1">
-      <c r="A73" s="15"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="21" t="s">
+      <c r="A73" s="65"/>
+      <c r="B73" s="66"/>
+      <c r="C73" s="66"/>
+      <c r="D73" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="E73" s="13"/>
-      <c r="F73" s="12"/>
-      <c r="G73" s="11"/>
-      <c r="H73" s="10"/>
+      <c r="E73" s="35"/>
+      <c r="F73" s="36"/>
+      <c r="G73" s="59"/>
+      <c r="H73" s="60"/>
     </row>
     <row r="74" spans="1:8" ht="9" customHeight="1">
-      <c r="A74" s="15"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="20" t="s">
+      <c r="A74" s="65"/>
+      <c r="B74" s="66"/>
+      <c r="C74" s="66"/>
+      <c r="D74" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="E74" s="19"/>
-      <c r="F74" s="18"/>
-      <c r="G74" s="17"/>
-      <c r="H74" s="16"/>
+      <c r="E74" s="70"/>
+      <c r="F74" s="71"/>
+      <c r="G74" s="61"/>
+      <c r="H74" s="62"/>
     </row>
     <row r="75" spans="1:8" ht="9" customHeight="1">
-      <c r="A75" s="15"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="13" t="s">
+      <c r="A75" s="65"/>
+      <c r="B75" s="66"/>
+      <c r="C75" s="66"/>
+      <c r="D75" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="E75" s="13"/>
-      <c r="F75" s="12"/>
-      <c r="G75" s="11"/>
-      <c r="H75" s="10"/>
+      <c r="E75" s="35"/>
+      <c r="F75" s="36"/>
+      <c r="G75" s="59"/>
+      <c r="H75" s="60"/>
     </row>
     <row r="76" spans="1:8" ht="9" customHeight="1" thickBot="1">
-      <c r="A76" s="9"/>
-      <c r="B76" s="8"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="7" t="s">
+      <c r="A76" s="67"/>
+      <c r="B76" s="68"/>
+      <c r="C76" s="68"/>
+      <c r="D76" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="E76" s="6"/>
-      <c r="F76" s="5"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="3"/>
+      <c r="E76" s="73"/>
+      <c r="F76" s="74"/>
+      <c r="G76" s="63"/>
+      <c r="H76" s="64"/>
     </row>
     <row r="77" spans="1:8" ht="9" customHeight="1" thickTop="1">
-      <c r="F77" s="2" t="s">
+      <c r="F77" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
+      <c r="G77" s="43"/>
+      <c r="H77" s="43"/>
     </row>
     <row r="78" spans="1:8" ht="9" customHeight="1">
       <c r="A78"/>
@@ -2332,78 +2338,16 @@
     <row r="85" customFormat="1"/>
   </sheetData>
   <mergeCells count="92">
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="D65:H65"/>
-    <mergeCell ref="D66:G66"/>
-    <mergeCell ref="D67:G67"/>
-    <mergeCell ref="D68:G68"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="G71:H72"/>
+    <mergeCell ref="G73:H74"/>
+    <mergeCell ref="G75:H76"/>
+    <mergeCell ref="A65:C76"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D72:F72"/>
     <mergeCell ref="F77:H77"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A21"/>
@@ -2414,16 +2358,78 @@
     <mergeCell ref="A58:A64"/>
     <mergeCell ref="D69:G69"/>
     <mergeCell ref="D70:G70"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="G71:H72"/>
-    <mergeCell ref="G73:H74"/>
-    <mergeCell ref="G75:H76"/>
-    <mergeCell ref="A65:C76"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="D65:H65"/>
+    <mergeCell ref="D66:G66"/>
+    <mergeCell ref="D67:G67"/>
+    <mergeCell ref="D68:G68"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:H4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.195138888888889" bottom="0" header="0" footer="0"/>

--- a/public/assets/templates/maintenance/utility.xlsx
+++ b/public/assets/templates/maintenance/utility.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B7E1CB7-2EE5-41A1-9FC1-1F3C45838383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC883E9-BDEC-4F87-B429-8A82104DB04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{FF133B37-4395-463D-9E0A-8A8115D83F24}"/>
   </bookViews>
@@ -814,6 +814,159 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -835,170 +988,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1382,28 +1382,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickTop="1">
-      <c r="A1" s="55"/>
-      <c r="B1" s="56"/>
-      <c r="C1" s="20" t="s">
+      <c r="A1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="71" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="21"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="57"/>
-      <c r="B2" s="58"/>
-      <c r="C2" s="22" t="s">
+      <c r="A2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="73" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="23"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:8" ht="10" customHeight="1">
       <c r="A3" s="19" t="s">
@@ -1413,15 +1413,15 @@
         <v>71</v>
       </c>
       <c r="C3" s="18"/>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="25" t="s">
+      <c r="E3" s="75"/>
+      <c r="F3" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="25"/>
-      <c r="H3" s="26"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="77"/>
     </row>
     <row r="4" spans="1:8" ht="10" customHeight="1">
       <c r="A4" s="19" t="s">
@@ -1431,875 +1431,875 @@
         <v>71</v>
       </c>
       <c r="C4" s="18"/>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="24"/>
-      <c r="F4" s="25" t="s">
+      <c r="E4" s="75"/>
+      <c r="F4" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="25"/>
-      <c r="H4" s="26"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="77"/>
     </row>
     <row r="5" spans="1:8" s="15" customFormat="1" ht="11" customHeight="1">
       <c r="A5" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="30"/>
+      <c r="C5" s="67"/>
       <c r="D5" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="33"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="70"/>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="46" t="s">
         <v>64</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="78"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="29"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="62"/>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A7" s="44"/>
+      <c r="A7" s="46"/>
       <c r="B7" s="10"/>
       <c r="C7" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="78"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="29"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="62"/>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A8" s="44"/>
+      <c r="A8" s="46"/>
       <c r="B8" s="10"/>
       <c r="C8" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="78"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="62"/>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A9" s="44"/>
+      <c r="A9" s="46"/>
       <c r="B9" s="10"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="29"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="62"/>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="47" t="s">
         <v>60</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="78"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="29"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="62"/>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A11" s="45"/>
+      <c r="A11" s="47"/>
       <c r="B11" s="10"/>
       <c r="C11" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="78"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="29"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="62"/>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A12" s="45"/>
+      <c r="A12" s="47"/>
       <c r="B12" s="10"/>
       <c r="C12" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="78"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="29"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="62"/>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A13" s="45"/>
+      <c r="A13" s="47"/>
       <c r="B13" s="10"/>
       <c r="C13" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="78"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="29"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="62"/>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A14" s="45"/>
+      <c r="A14" s="47"/>
       <c r="B14" s="10"/>
       <c r="C14" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="78"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="29"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="62"/>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A15" s="45"/>
+      <c r="A15" s="47"/>
       <c r="B15" s="10"/>
       <c r="C15" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="78"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="29"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="62"/>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A16" s="45"/>
+      <c r="A16" s="47"/>
       <c r="B16" s="10"/>
       <c r="C16" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="78"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="29"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="62"/>
     </row>
     <row r="17" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A17" s="45"/>
+      <c r="A17" s="47"/>
       <c r="B17" s="10"/>
       <c r="C17" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="78"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="29"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="62"/>
       <c r="J17" s="6" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A18" s="45"/>
+      <c r="A18" s="47"/>
       <c r="B18" s="10"/>
       <c r="C18" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="78"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="29"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="62"/>
     </row>
     <row r="19" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A19" s="45"/>
+      <c r="A19" s="47"/>
       <c r="B19" s="10"/>
       <c r="C19" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="78"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="29"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="62"/>
     </row>
     <row r="20" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A20" s="45"/>
+      <c r="A20" s="47"/>
       <c r="B20" s="10"/>
       <c r="C20" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="78"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="29"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="66"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="62"/>
     </row>
     <row r="21" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A21" s="45"/>
+      <c r="A21" s="47"/>
       <c r="B21" s="10"/>
-      <c r="D21" s="78"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="29"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="66"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="62"/>
     </row>
     <row r="22" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A22" s="46" t="s">
+      <c r="A22" s="48" t="s">
         <v>47</v>
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="78"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="29"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="62"/>
       <c r="J22" s="13"/>
     </row>
     <row r="23" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A23" s="46"/>
+      <c r="A23" s="48"/>
       <c r="B23" s="10"/>
       <c r="C23" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D23" s="78"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="29"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="62"/>
     </row>
     <row r="24" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A24" s="46"/>
+      <c r="A24" s="48"/>
       <c r="B24" s="10"/>
       <c r="C24" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="78"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="29"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="66"/>
+      <c r="F24" s="61"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="62"/>
     </row>
     <row r="25" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A25" s="46"/>
+      <c r="A25" s="48"/>
       <c r="B25" s="10"/>
       <c r="C25" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="78"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="29"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="66"/>
+      <c r="F25" s="61"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="62"/>
     </row>
     <row r="26" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A26" s="46"/>
+      <c r="A26" s="48"/>
       <c r="B26" s="10"/>
       <c r="C26" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="78"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="29"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="62"/>
     </row>
     <row r="27" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A27" s="46"/>
+      <c r="A27" s="48"/>
       <c r="B27" s="10"/>
       <c r="C27" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="78"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="29"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="61"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="62"/>
     </row>
     <row r="28" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A28" s="46"/>
+      <c r="A28" s="48"/>
       <c r="B28" s="10"/>
       <c r="C28" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D28" s="78"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="29"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="66"/>
+      <c r="F28" s="61"/>
+      <c r="G28" s="61"/>
+      <c r="H28" s="62"/>
     </row>
     <row r="29" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A29" s="46"/>
+      <c r="A29" s="48"/>
       <c r="B29" s="10"/>
       <c r="C29" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D29" s="78"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="29"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="66"/>
+      <c r="F29" s="61"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="62"/>
     </row>
     <row r="30" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A30" s="46"/>
+      <c r="A30" s="48"/>
       <c r="B30" s="10"/>
       <c r="C30" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D30" s="78"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="29"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="66"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="62"/>
     </row>
     <row r="31" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="48" t="s">
         <v>37</v>
       </c>
       <c r="B31" s="10"/>
       <c r="C31" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D31" s="78"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="29"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="66"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="62"/>
     </row>
     <row r="32" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A32" s="46"/>
+      <c r="A32" s="48"/>
       <c r="B32" s="10"/>
       <c r="C32" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="78"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="29"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="66"/>
+      <c r="F32" s="61"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="62"/>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A33" s="46"/>
+      <c r="A33" s="48"/>
       <c r="B33" s="8"/>
       <c r="C33" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="79"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="29"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="66"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="61"/>
+      <c r="H33" s="62"/>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A34" s="46"/>
+      <c r="A34" s="48"/>
       <c r="B34" s="8"/>
       <c r="C34" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="79"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="29"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="66"/>
+      <c r="F34" s="61"/>
+      <c r="G34" s="61"/>
+      <c r="H34" s="62"/>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A35" s="46"/>
+      <c r="A35" s="48"/>
       <c r="B35" s="8"/>
-      <c r="D35" s="79"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="29"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="61"/>
+      <c r="G35" s="61"/>
+      <c r="H35" s="62"/>
     </row>
     <row r="36" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A36" s="47" t="s">
+      <c r="A36" s="49" t="s">
         <v>32</v>
       </c>
       <c r="B36" s="10"/>
       <c r="C36" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D36" s="78"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="29"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="66"/>
+      <c r="F36" s="61"/>
+      <c r="G36" s="61"/>
+      <c r="H36" s="62"/>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A37" s="48"/>
+      <c r="A37" s="50"/>
       <c r="B37" s="10"/>
       <c r="C37" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D37" s="78"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="29"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="66"/>
+      <c r="F37" s="61"/>
+      <c r="G37" s="61"/>
+      <c r="H37" s="62"/>
     </row>
     <row r="38" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A38" s="48"/>
+      <c r="A38" s="50"/>
       <c r="B38" s="10"/>
       <c r="C38" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D38" s="78"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="29"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="66"/>
+      <c r="F38" s="61"/>
+      <c r="G38" s="61"/>
+      <c r="H38" s="62"/>
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A39" s="48"/>
+      <c r="A39" s="50"/>
       <c r="B39" s="10"/>
       <c r="C39" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D39" s="78"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="29"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="61"/>
+      <c r="G39" s="61"/>
+      <c r="H39" s="62"/>
     </row>
     <row r="40" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A40" s="48"/>
+      <c r="A40" s="50"/>
       <c r="B40" s="10"/>
       <c r="C40" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D40" s="78"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="29"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="66"/>
+      <c r="F40" s="61"/>
+      <c r="G40" s="61"/>
+      <c r="H40" s="62"/>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A41" s="48"/>
+      <c r="A41" s="50"/>
       <c r="B41" s="10"/>
       <c r="C41" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D41" s="78"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="29"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="66"/>
+      <c r="F41" s="61"/>
+      <c r="G41" s="61"/>
+      <c r="H41" s="62"/>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A42" s="48"/>
+      <c r="A42" s="50"/>
       <c r="B42" s="10"/>
       <c r="C42" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D42" s="78"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="29"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="66"/>
+      <c r="F42" s="61"/>
+      <c r="G42" s="61"/>
+      <c r="H42" s="62"/>
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A43" s="48"/>
+      <c r="A43" s="50"/>
       <c r="B43" s="10"/>
       <c r="C43" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D43" s="78"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="29"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="61"/>
+      <c r="G43" s="61"/>
+      <c r="H43" s="62"/>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A44" s="48"/>
+      <c r="A44" s="50"/>
       <c r="B44" s="10"/>
       <c r="C44" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D44" s="78"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="29"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="66"/>
+      <c r="F44" s="61"/>
+      <c r="G44" s="61"/>
+      <c r="H44" s="62"/>
     </row>
     <row r="45" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A45" s="48"/>
+      <c r="A45" s="50"/>
       <c r="B45" s="10"/>
       <c r="C45" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D45" s="78"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="29"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="66"/>
+      <c r="F45" s="61"/>
+      <c r="G45" s="61"/>
+      <c r="H45" s="62"/>
     </row>
     <row r="46" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A46" s="48"/>
+      <c r="A46" s="50"/>
       <c r="B46" s="10"/>
       <c r="C46" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D46" s="78"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="29"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="66"/>
+      <c r="F46" s="61"/>
+      <c r="G46" s="61"/>
+      <c r="H46" s="62"/>
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A47" s="48"/>
+      <c r="A47" s="50"/>
       <c r="B47" s="10"/>
       <c r="C47" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D47" s="78"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="29"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="61"/>
+      <c r="G47" s="61"/>
+      <c r="H47" s="62"/>
     </row>
     <row r="48" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A48" s="48"/>
+      <c r="A48" s="50"/>
       <c r="B48" s="10"/>
       <c r="C48" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D48" s="78"/>
-      <c r="E48" s="27"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="29"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="66"/>
+      <c r="F48" s="61"/>
+      <c r="G48" s="61"/>
+      <c r="H48" s="62"/>
     </row>
     <row r="49" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A49" s="48"/>
+      <c r="A49" s="50"/>
       <c r="B49" s="10"/>
       <c r="C49" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D49" s="78"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="29"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="66"/>
+      <c r="F49" s="61"/>
+      <c r="G49" s="61"/>
+      <c r="H49" s="62"/>
     </row>
     <row r="50" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A50" s="48"/>
+      <c r="A50" s="50"/>
       <c r="B50" s="10"/>
       <c r="C50" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D50" s="78"/>
-      <c r="E50" s="27"/>
-      <c r="F50" s="28"/>
-      <c r="G50" s="28"/>
-      <c r="H50" s="29"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="66"/>
+      <c r="F50" s="61"/>
+      <c r="G50" s="61"/>
+      <c r="H50" s="62"/>
     </row>
     <row r="51" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A51" s="48"/>
+      <c r="A51" s="50"/>
       <c r="B51" s="10"/>
       <c r="C51" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D51" s="78"/>
-      <c r="E51" s="27"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="29"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="66"/>
+      <c r="F51" s="61"/>
+      <c r="G51" s="61"/>
+      <c r="H51" s="62"/>
     </row>
     <row r="52" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A52" s="49"/>
+      <c r="A52" s="51"/>
       <c r="B52" s="10"/>
-      <c r="D52" s="78"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="29"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="66"/>
+      <c r="F52" s="61"/>
+      <c r="G52" s="61"/>
+      <c r="H52" s="62"/>
     </row>
     <row r="53" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A53" s="50" t="s">
+      <c r="A53" s="52" t="s">
         <v>15</v>
       </c>
       <c r="B53" s="10"/>
       <c r="C53" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D53" s="78"/>
-      <c r="E53" s="27"/>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="29"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="66"/>
+      <c r="F53" s="61"/>
+      <c r="G53" s="61"/>
+      <c r="H53" s="62"/>
     </row>
     <row r="54" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A54" s="50"/>
+      <c r="A54" s="52"/>
       <c r="B54" s="8"/>
       <c r="C54" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D54" s="79"/>
-      <c r="E54" s="27"/>
-      <c r="F54" s="28"/>
-      <c r="G54" s="28"/>
-      <c r="H54" s="29"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="66"/>
+      <c r="F54" s="61"/>
+      <c r="G54" s="61"/>
+      <c r="H54" s="62"/>
     </row>
     <row r="55" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A55" s="50"/>
+      <c r="A55" s="52"/>
       <c r="B55" s="8"/>
       <c r="C55" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D55" s="79"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="28"/>
-      <c r="H55" s="29"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="66"/>
+      <c r="F55" s="61"/>
+      <c r="G55" s="61"/>
+      <c r="H55" s="62"/>
     </row>
     <row r="56" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A56" s="50"/>
+      <c r="A56" s="52"/>
       <c r="B56" s="8"/>
       <c r="C56" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D56" s="79"/>
-      <c r="E56" s="27"/>
-      <c r="F56" s="28"/>
-      <c r="G56" s="28"/>
-      <c r="H56" s="29"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="66"/>
+      <c r="F56" s="61"/>
+      <c r="G56" s="61"/>
+      <c r="H56" s="62"/>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A57" s="50"/>
+      <c r="A57" s="52"/>
       <c r="B57" s="8"/>
-      <c r="D57" s="79"/>
-      <c r="E57" s="28"/>
-      <c r="F57" s="28"/>
-      <c r="G57" s="28"/>
-      <c r="H57" s="29"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="61"/>
+      <c r="F57" s="61"/>
+      <c r="G57" s="61"/>
+      <c r="H57" s="62"/>
     </row>
     <row r="58" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A58" s="51"/>
+      <c r="A58" s="53"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
-      <c r="D58" s="80"/>
-      <c r="E58" s="28"/>
-      <c r="F58" s="28"/>
-      <c r="G58" s="28"/>
-      <c r="H58" s="29"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="61"/>
+      <c r="F58" s="61"/>
+      <c r="G58" s="61"/>
+      <c r="H58" s="62"/>
     </row>
     <row r="59" spans="1:8" ht="9" customHeight="1">
-      <c r="A59" s="51"/>
+      <c r="A59" s="53"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
-      <c r="D59" s="80"/>
-      <c r="E59" s="28"/>
-      <c r="F59" s="28"/>
-      <c r="G59" s="28"/>
-      <c r="H59" s="29"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="61"/>
+      <c r="F59" s="61"/>
+      <c r="G59" s="61"/>
+      <c r="H59" s="62"/>
     </row>
     <row r="60" spans="1:8" ht="9" customHeight="1">
-      <c r="A60" s="51"/>
+      <c r="A60" s="53"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
-      <c r="D60" s="80"/>
-      <c r="E60" s="28"/>
-      <c r="F60" s="28"/>
-      <c r="G60" s="28"/>
-      <c r="H60" s="29"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="61"/>
+      <c r="F60" s="61"/>
+      <c r="G60" s="61"/>
+      <c r="H60" s="62"/>
     </row>
     <row r="61" spans="1:8" ht="9" customHeight="1">
-      <c r="A61" s="51"/>
+      <c r="A61" s="53"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
-      <c r="D61" s="81"/>
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
-      <c r="H61" s="29"/>
+      <c r="D61" s="23"/>
+      <c r="E61" s="61"/>
+      <c r="F61" s="61"/>
+      <c r="G61" s="61"/>
+      <c r="H61" s="62"/>
     </row>
     <row r="62" spans="1:8" ht="9" customHeight="1">
-      <c r="A62" s="51"/>
+      <c r="A62" s="53"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
-      <c r="D62" s="81"/>
-      <c r="E62" s="28"/>
-      <c r="F62" s="28"/>
-      <c r="G62" s="28"/>
-      <c r="H62" s="29"/>
+      <c r="D62" s="23"/>
+      <c r="E62" s="61"/>
+      <c r="F62" s="61"/>
+      <c r="G62" s="61"/>
+      <c r="H62" s="62"/>
     </row>
     <row r="63" spans="1:8" ht="9" customHeight="1">
-      <c r="A63" s="51"/>
+      <c r="A63" s="53"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
-      <c r="D63" s="81"/>
-      <c r="E63" s="28"/>
-      <c r="F63" s="28"/>
-      <c r="G63" s="28"/>
-      <c r="H63" s="29"/>
+      <c r="D63" s="23"/>
+      <c r="E63" s="61"/>
+      <c r="F63" s="61"/>
+      <c r="G63" s="61"/>
+      <c r="H63" s="62"/>
     </row>
     <row r="64" spans="1:8" ht="9" customHeight="1">
-      <c r="A64" s="52"/>
+      <c r="A64" s="54"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
-      <c r="D64" s="81"/>
-      <c r="E64" s="28"/>
-      <c r="F64" s="28"/>
-      <c r="G64" s="28"/>
-      <c r="H64" s="29"/>
+      <c r="D64" s="23"/>
+      <c r="E64" s="61"/>
+      <c r="F64" s="61"/>
+      <c r="G64" s="61"/>
+      <c r="H64" s="62"/>
     </row>
     <row r="65" spans="1:8" ht="9" customHeight="1">
-      <c r="A65" s="65" t="s">
+      <c r="A65" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="B65" s="66"/>
-      <c r="C65" s="66"/>
-      <c r="D65" s="37" t="s">
+      <c r="B65" s="79"/>
+      <c r="C65" s="79"/>
+      <c r="D65" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="E65" s="37"/>
-      <c r="F65" s="37"/>
-      <c r="G65" s="37"/>
-      <c r="H65" s="38"/>
+      <c r="E65" s="63"/>
+      <c r="F65" s="63"/>
+      <c r="G65" s="63"/>
+      <c r="H65" s="64"/>
     </row>
     <row r="66" spans="1:8" ht="9" customHeight="1">
-      <c r="A66" s="65"/>
-      <c r="B66" s="66"/>
-      <c r="C66" s="66"/>
-      <c r="D66" s="37" t="s">
+      <c r="A66" s="78"/>
+      <c r="B66" s="79"/>
+      <c r="C66" s="79"/>
+      <c r="D66" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="E66" s="37"/>
-      <c r="F66" s="37"/>
-      <c r="G66" s="39"/>
+      <c r="E66" s="63"/>
+      <c r="F66" s="63"/>
+      <c r="G66" s="65"/>
       <c r="H66" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="9" customHeight="1">
-      <c r="A67" s="65"/>
-      <c r="B67" s="66"/>
-      <c r="C67" s="66"/>
-      <c r="D67" s="40"/>
-      <c r="E67" s="41"/>
-      <c r="F67" s="41"/>
-      <c r="G67" s="42"/>
+      <c r="A67" s="78"/>
+      <c r="B67" s="79"/>
+      <c r="C67" s="79"/>
+      <c r="D67" s="55"/>
+      <c r="E67" s="56"/>
+      <c r="F67" s="56"/>
+      <c r="G67" s="57"/>
       <c r="H67" s="2"/>
     </row>
     <row r="68" spans="1:8" ht="9" customHeight="1">
-      <c r="A68" s="65"/>
-      <c r="B68" s="66"/>
-      <c r="C68" s="66"/>
-      <c r="D68" s="40"/>
-      <c r="E68" s="41"/>
-      <c r="F68" s="41"/>
-      <c r="G68" s="42"/>
+      <c r="A68" s="78"/>
+      <c r="B68" s="79"/>
+      <c r="C68" s="79"/>
+      <c r="D68" s="55"/>
+      <c r="E68" s="56"/>
+      <c r="F68" s="56"/>
+      <c r="G68" s="57"/>
       <c r="H68" s="2"/>
     </row>
     <row r="69" spans="1:8" ht="9" customHeight="1">
-      <c r="A69" s="65"/>
-      <c r="B69" s="66"/>
-      <c r="C69" s="66"/>
-      <c r="D69" s="40"/>
-      <c r="E69" s="41"/>
-      <c r="F69" s="41"/>
-      <c r="G69" s="42"/>
+      <c r="A69" s="78"/>
+      <c r="B69" s="79"/>
+      <c r="C69" s="79"/>
+      <c r="D69" s="55"/>
+      <c r="E69" s="56"/>
+      <c r="F69" s="56"/>
+      <c r="G69" s="57"/>
       <c r="H69" s="2"/>
     </row>
     <row r="70" spans="1:8" ht="9" customHeight="1">
-      <c r="A70" s="65"/>
-      <c r="B70" s="66"/>
-      <c r="C70" s="66"/>
-      <c r="D70" s="53"/>
-      <c r="E70" s="54"/>
-      <c r="F70" s="54"/>
-      <c r="G70" s="42"/>
+      <c r="A70" s="78"/>
+      <c r="B70" s="79"/>
+      <c r="C70" s="79"/>
+      <c r="D70" s="58"/>
+      <c r="E70" s="59"/>
+      <c r="F70" s="59"/>
+      <c r="G70" s="57"/>
       <c r="H70" s="2"/>
     </row>
     <row r="71" spans="1:8" ht="9" customHeight="1">
-      <c r="A71" s="65"/>
-      <c r="B71" s="66"/>
-      <c r="C71" s="66"/>
-      <c r="D71" s="75" t="s">
+      <c r="A71" s="78"/>
+      <c r="B71" s="79"/>
+      <c r="C71" s="79"/>
+      <c r="D71" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="E71" s="76"/>
-      <c r="F71" s="77"/>
-      <c r="G71" s="59"/>
-      <c r="H71" s="60"/>
+      <c r="E71" s="43"/>
+      <c r="F71" s="44"/>
+      <c r="G71" s="28"/>
+      <c r="H71" s="29"/>
     </row>
     <row r="72" spans="1:8" ht="9" customHeight="1">
-      <c r="A72" s="65"/>
-      <c r="B72" s="66"/>
-      <c r="C72" s="66"/>
-      <c r="D72" s="69" t="s">
+      <c r="A72" s="78"/>
+      <c r="B72" s="79"/>
+      <c r="C72" s="79"/>
+      <c r="D72" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="E72" s="70"/>
-      <c r="F72" s="71"/>
-      <c r="G72" s="61"/>
-      <c r="H72" s="62"/>
+      <c r="E72" s="35"/>
+      <c r="F72" s="36"/>
+      <c r="G72" s="30"/>
+      <c r="H72" s="31"/>
     </row>
     <row r="73" spans="1:8" ht="9" customHeight="1">
-      <c r="A73" s="65"/>
-      <c r="B73" s="66"/>
-      <c r="C73" s="66"/>
-      <c r="D73" s="34" t="s">
+      <c r="A73" s="78"/>
+      <c r="B73" s="79"/>
+      <c r="C73" s="79"/>
+      <c r="D73" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="E73" s="35"/>
-      <c r="F73" s="36"/>
-      <c r="G73" s="59"/>
-      <c r="H73" s="60"/>
+      <c r="E73" s="37"/>
+      <c r="F73" s="38"/>
+      <c r="G73" s="28"/>
+      <c r="H73" s="29"/>
     </row>
     <row r="74" spans="1:8" ht="9" customHeight="1">
-      <c r="A74" s="65"/>
-      <c r="B74" s="66"/>
-      <c r="C74" s="66"/>
-      <c r="D74" s="69" t="s">
+      <c r="A74" s="78"/>
+      <c r="B74" s="79"/>
+      <c r="C74" s="79"/>
+      <c r="D74" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="E74" s="70"/>
-      <c r="F74" s="71"/>
-      <c r="G74" s="61"/>
-      <c r="H74" s="62"/>
+      <c r="E74" s="35"/>
+      <c r="F74" s="36"/>
+      <c r="G74" s="30"/>
+      <c r="H74" s="31"/>
     </row>
     <row r="75" spans="1:8" ht="9" customHeight="1">
-      <c r="A75" s="65"/>
-      <c r="B75" s="66"/>
-      <c r="C75" s="66"/>
-      <c r="D75" s="35" t="s">
+      <c r="A75" s="78"/>
+      <c r="B75" s="79"/>
+      <c r="C75" s="79"/>
+      <c r="D75" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="E75" s="35"/>
-      <c r="F75" s="36"/>
-      <c r="G75" s="59"/>
-      <c r="H75" s="60"/>
+      <c r="E75" s="37"/>
+      <c r="F75" s="38"/>
+      <c r="G75" s="28"/>
+      <c r="H75" s="29"/>
     </row>
     <row r="76" spans="1:8" ht="9" customHeight="1" thickBot="1">
-      <c r="A76" s="67"/>
-      <c r="B76" s="68"/>
-      <c r="C76" s="68"/>
-      <c r="D76" s="72" t="s">
+      <c r="A76" s="80"/>
+      <c r="B76" s="81"/>
+      <c r="C76" s="81"/>
+      <c r="D76" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="E76" s="73"/>
-      <c r="F76" s="74"/>
-      <c r="G76" s="63"/>
-      <c r="H76" s="64"/>
+      <c r="E76" s="40"/>
+      <c r="F76" s="41"/>
+      <c r="G76" s="32"/>
+      <c r="H76" s="33"/>
     </row>
     <row r="77" spans="1:8" ht="9" customHeight="1" thickTop="1">
-      <c r="F77" s="43" t="s">
+      <c r="F77" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="G77" s="43"/>
-      <c r="H77" s="43"/>
+      <c r="G77" s="45"/>
+      <c r="H77" s="45"/>
     </row>
     <row r="78" spans="1:8" ht="9" customHeight="1">
       <c r="A78"/>
@@ -2338,16 +2338,66 @@
     <row r="85" customFormat="1"/>
   </sheetData>
   <mergeCells count="92">
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="G71:H72"/>
-    <mergeCell ref="G73:H74"/>
-    <mergeCell ref="G75:H76"/>
-    <mergeCell ref="A65:C76"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E53:H53"/>
     <mergeCell ref="F77:H77"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A21"/>
@@ -2364,72 +2414,22 @@
     <mergeCell ref="D66:G66"/>
     <mergeCell ref="D67:G67"/>
     <mergeCell ref="D68:G68"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="G71:H72"/>
+    <mergeCell ref="G73:H74"/>
+    <mergeCell ref="G75:H76"/>
+    <mergeCell ref="A65:C76"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D72:F72"/>
     <mergeCell ref="E54:H54"/>
     <mergeCell ref="E55:H55"/>
     <mergeCell ref="E56:H56"/>
     <mergeCell ref="E57:H57"/>
     <mergeCell ref="E58:H58"/>
     <mergeCell ref="E59:H59"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:H4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.195138888888889" bottom="0" header="0" footer="0"/>

--- a/public/assets/templates/maintenance/utility.xlsx
+++ b/public/assets/templates/maintenance/utility.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC883E9-BDEC-4F87-B429-8A82104DB04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFC1418-E339-47D8-ADF6-7537737A7657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{FF133B37-4395-463D-9E0A-8A8115D83F24}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="UTILITY" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">UTILITY!$A$1:$H$77</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">UTILITY!$A$1:$H$79</definedName>
   </definedNames>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="82">
   <si>
     <t>FRM/EUT/01/009/003-02</t>
   </si>
@@ -252,14 +252,28 @@
     <t>Nama Mesin</t>
   </si>
   <si>
-    <t xml:space="preserve">Tanggal 
-</t>
-  </si>
-  <si>
     <t>PT BUMI ALAM SEGAR</t>
   </si>
   <si>
     <t>LAPORAN MAINTENANCE UTILITY</t>
+  </si>
+  <si>
+    <t>Tanggal</t>
+  </si>
+  <si>
+    <t>Waktu Mulai</t>
+  </si>
+  <si>
+    <t>Waktu Selesai</t>
+  </si>
+  <si>
+    <t>Kode Mesin</t>
+  </si>
+  <si>
+    <t>Lokasi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">: </t>
   </si>
 </sst>
 </file>
@@ -826,6 +840,111 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -856,6 +975,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -865,12 +996,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -888,117 +1013,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1367,7 +1381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FD37B8E-471E-41A7-B580-DEEAA14201F7}">
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="10.1796875" style="1" customWidth="1"/>
@@ -1382,946 +1396,962 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickTop="1">
-      <c r="A1" s="24"/>
-      <c r="B1" s="25"/>
-      <c r="C1" s="71" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="59"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="26"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="73" t="s">
-        <v>75</v>
-      </c>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="1:8" ht="10" customHeight="1">
       <c r="A3" s="19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B3" s="18" t="s">
         <v>71</v>
       </c>
       <c r="C3" s="18"/>
-      <c r="D3" s="75" t="s">
+      <c r="D3" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="E3" s="75"/>
-      <c r="F3" s="76" t="s">
+      <c r="E3" s="28"/>
+      <c r="F3" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="76"/>
-      <c r="H3" s="77"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="30"/>
     </row>
     <row r="4" spans="1:8" ht="10" customHeight="1">
       <c r="A4" s="19" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B4" s="18" t="s">
         <v>71</v>
       </c>
       <c r="C4" s="18"/>
-      <c r="D4" s="75" t="s">
+      <c r="D4" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="28"/>
+      <c r="F4" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" s="29"/>
+      <c r="H4" s="30"/>
+    </row>
+    <row r="5" spans="1:8" ht="10" customHeight="1">
+      <c r="A5" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="18"/>
+      <c r="D5" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="28"/>
+      <c r="F5" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="29"/>
+      <c r="H5" s="30"/>
+    </row>
+    <row r="6" spans="1:8" ht="10" customHeight="1">
+      <c r="A6" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="18"/>
+      <c r="D6" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="75"/>
-      <c r="F4" s="76" t="s">
+      <c r="E6" s="28"/>
+      <c r="F6" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="76"/>
-      <c r="H4" s="77"/>
-    </row>
-    <row r="5" spans="1:8" s="15" customFormat="1" ht="11" customHeight="1">
-      <c r="A5" s="17" t="s">
+      <c r="G6" s="29"/>
+      <c r="H6" s="30"/>
+    </row>
+    <row r="7" spans="1:8" s="15" customFormat="1" ht="11" customHeight="1">
+      <c r="A7" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="67" t="s">
+      <c r="B7" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="67"/>
-      <c r="D5" s="16" t="s">
+      <c r="C7" s="34"/>
+      <c r="D7" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="68" t="s">
+      <c r="E7" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="70"/>
-    </row>
-    <row r="6" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A6" s="46" t="s">
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="37"/>
+    </row>
+    <row r="8" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A8" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="62"/>
-    </row>
-    <row r="7" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A7" s="46"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="62"/>
-    </row>
-    <row r="8" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A8" s="46"/>
       <c r="B8" s="10"/>
       <c r="C8" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D8" s="20"/>
-      <c r="E8" s="66"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="62"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="33"/>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A9" s="46"/>
+      <c r="A9" s="39"/>
       <c r="B9" s="10"/>
+      <c r="C9" s="12" t="s">
+        <v>62</v>
+      </c>
       <c r="D9" s="20"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="62"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="33"/>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A10" s="47" t="s">
-        <v>60</v>
-      </c>
+      <c r="A10" s="39"/>
       <c r="B10" s="10"/>
       <c r="C10" s="12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D10" s="20"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="62"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="33"/>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A11" s="47"/>
+      <c r="A11" s="39"/>
       <c r="B11" s="10"/>
-      <c r="C11" s="12" t="s">
-        <v>58</v>
-      </c>
       <c r="D11" s="20"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="62"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="33"/>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A12" s="47"/>
+      <c r="A12" s="40" t="s">
+        <v>60</v>
+      </c>
       <c r="B12" s="10"/>
       <c r="C12" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D12" s="20"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="62"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="33"/>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A13" s="47"/>
+      <c r="A13" s="40"/>
       <c r="B13" s="10"/>
       <c r="C13" s="12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D13" s="20"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="62"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="33"/>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A14" s="47"/>
+      <c r="A14" s="40"/>
       <c r="B14" s="10"/>
       <c r="C14" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" s="20"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="62"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="33"/>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A15" s="47"/>
+      <c r="A15" s="40"/>
       <c r="B15" s="10"/>
       <c r="C15" s="12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" s="20"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="62"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="33"/>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A16" s="47"/>
+      <c r="A16" s="40"/>
       <c r="B16" s="10"/>
       <c r="C16" s="12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" s="20"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="62"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="33"/>
     </row>
     <row r="17" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A17" s="47"/>
+      <c r="A17" s="40"/>
       <c r="B17" s="10"/>
       <c r="C17" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D17" s="20"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="61"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="62"/>
-      <c r="J17" s="6" t="s">
-        <v>51</v>
-      </c>
+      <c r="E17" s="31"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="33"/>
     </row>
     <row r="18" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A18" s="47"/>
+      <c r="A18" s="40"/>
       <c r="B18" s="10"/>
       <c r="C18" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="20"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="33"/>
+    </row>
+    <row r="19" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A19" s="40"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="20"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="33"/>
+      <c r="J19" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A20" s="40"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="20"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="62"/>
-    </row>
-    <row r="19" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A19" s="47"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="14" t="s">
+      <c r="D20" s="20"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="33"/>
+    </row>
+    <row r="21" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A21" s="40"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="20"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="62"/>
-    </row>
-    <row r="20" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A20" s="47"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="14" t="s">
+      <c r="D21" s="20"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="33"/>
+    </row>
+    <row r="22" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A22" s="40"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="62"/>
-    </row>
-    <row r="21" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A21" s="47"/>
-      <c r="B21" s="10"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="66"/>
-      <c r="F21" s="61"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="62"/>
-    </row>
-    <row r="22" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A22" s="48" t="s">
+      <c r="D22" s="20"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="33"/>
+    </row>
+    <row r="23" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A23" s="40"/>
+      <c r="B23" s="10"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="33"/>
+    </row>
+    <row r="24" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A24" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="61"/>
-      <c r="H22" s="62"/>
-      <c r="J22" s="13"/>
-    </row>
-    <row r="23" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A23" s="48"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="61"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="62"/>
-    </row>
-    <row r="24" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A24" s="48"/>
       <c r="B24" s="10"/>
       <c r="C24" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D24" s="20"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="61"/>
-      <c r="G24" s="61"/>
-      <c r="H24" s="62"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="33"/>
+      <c r="J24" s="13"/>
     </row>
     <row r="25" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A25" s="48"/>
+      <c r="A25" s="41"/>
       <c r="B25" s="10"/>
       <c r="C25" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D25" s="20"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="61"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="62"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="33"/>
     </row>
     <row r="26" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A26" s="48"/>
+      <c r="A26" s="41"/>
       <c r="B26" s="10"/>
       <c r="C26" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D26" s="20"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="61"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="62"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="33"/>
     </row>
     <row r="27" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A27" s="48"/>
+      <c r="A27" s="41"/>
       <c r="B27" s="10"/>
       <c r="C27" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D27" s="20"/>
-      <c r="E27" s="66"/>
-      <c r="F27" s="61"/>
-      <c r="G27" s="61"/>
-      <c r="H27" s="62"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="33"/>
     </row>
     <row r="28" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A28" s="48"/>
+      <c r="A28" s="41"/>
       <c r="B28" s="10"/>
       <c r="C28" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D28" s="20"/>
-      <c r="E28" s="66"/>
-      <c r="F28" s="61"/>
-      <c r="G28" s="61"/>
-      <c r="H28" s="62"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="33"/>
     </row>
     <row r="29" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A29" s="48"/>
+      <c r="A29" s="41"/>
       <c r="B29" s="10"/>
       <c r="C29" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D29" s="20"/>
-      <c r="E29" s="66"/>
-      <c r="F29" s="61"/>
-      <c r="G29" s="61"/>
-      <c r="H29" s="62"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="33"/>
     </row>
     <row r="30" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A30" s="48"/>
+      <c r="A30" s="41"/>
       <c r="B30" s="10"/>
       <c r="C30" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="20"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="33"/>
+    </row>
+    <row r="31" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A31" s="41"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="20"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="33"/>
+    </row>
+    <row r="32" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A32" s="41"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="66"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="62"/>
-    </row>
-    <row r="31" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A31" s="48" t="s">
+      <c r="D32" s="20"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="33"/>
+    </row>
+    <row r="33" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A33" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="10"/>
-      <c r="C31" s="11" t="s">
+      <c r="B33" s="10"/>
+      <c r="C33" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="66"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="62"/>
-    </row>
-    <row r="32" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A32" s="48"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="11" t="s">
+      <c r="D33" s="20"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="33"/>
+    </row>
+    <row r="34" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A34" s="41"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="20"/>
-      <c r="E32" s="66"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="62"/>
-    </row>
-    <row r="33" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A33" s="48"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="11" t="s">
+      <c r="D34" s="20"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="33"/>
+    </row>
+    <row r="35" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A35" s="41"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="21"/>
-      <c r="E33" s="66"/>
-      <c r="F33" s="61"/>
-      <c r="G33" s="61"/>
-      <c r="H33" s="62"/>
-    </row>
-    <row r="34" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A34" s="48"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="11" t="s">
+      <c r="D35" s="21"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="33"/>
+    </row>
+    <row r="36" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A36" s="41"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="21"/>
-      <c r="E34" s="66"/>
-      <c r="F34" s="61"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="62"/>
-    </row>
-    <row r="35" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A35" s="48"/>
-      <c r="B35" s="8"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="66"/>
-      <c r="F35" s="61"/>
-      <c r="G35" s="61"/>
-      <c r="H35" s="62"/>
-    </row>
-    <row r="36" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A36" s="49" t="s">
+      <c r="D36" s="21"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="33"/>
+    </row>
+    <row r="37" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A37" s="41"/>
+      <c r="B37" s="8"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="33"/>
+    </row>
+    <row r="38" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A38" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="B36" s="10"/>
-      <c r="C36" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="66"/>
-      <c r="F36" s="61"/>
-      <c r="G36" s="61"/>
-      <c r="H36" s="62"/>
-    </row>
-    <row r="37" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A37" s="50"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" s="20"/>
-      <c r="E37" s="66"/>
-      <c r="F37" s="61"/>
-      <c r="G37" s="61"/>
-      <c r="H37" s="62"/>
-    </row>
-    <row r="38" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A38" s="50"/>
       <c r="B38" s="10"/>
       <c r="C38" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D38" s="20"/>
-      <c r="E38" s="66"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="61"/>
-      <c r="H38" s="62"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="33"/>
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A39" s="50"/>
+      <c r="A39" s="43"/>
       <c r="B39" s="10"/>
       <c r="C39" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D39" s="20"/>
-      <c r="E39" s="66"/>
-      <c r="F39" s="61"/>
-      <c r="G39" s="61"/>
-      <c r="H39" s="62"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="33"/>
     </row>
     <row r="40" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A40" s="50"/>
+      <c r="A40" s="43"/>
       <c r="B40" s="10"/>
       <c r="C40" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D40" s="20"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="62"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="33"/>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A41" s="50"/>
+      <c r="A41" s="43"/>
       <c r="B41" s="10"/>
       <c r="C41" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D41" s="20"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="61"/>
-      <c r="G41" s="61"/>
-      <c r="H41" s="62"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="33"/>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A42" s="50"/>
+      <c r="A42" s="43"/>
       <c r="B42" s="10"/>
       <c r="C42" s="9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D42" s="20"/>
-      <c r="E42" s="66"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="61"/>
-      <c r="H42" s="62"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="33"/>
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A43" s="50"/>
+      <c r="A43" s="43"/>
       <c r="B43" s="10"/>
       <c r="C43" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D43" s="20"/>
-      <c r="E43" s="66"/>
-      <c r="F43" s="61"/>
-      <c r="G43" s="61"/>
-      <c r="H43" s="62"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="33"/>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A44" s="50"/>
+      <c r="A44" s="43"/>
       <c r="B44" s="10"/>
       <c r="C44" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D44" s="20"/>
-      <c r="E44" s="66"/>
-      <c r="F44" s="61"/>
-      <c r="G44" s="61"/>
-      <c r="H44" s="62"/>
+      <c r="E44" s="31"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="33"/>
     </row>
     <row r="45" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A45" s="50"/>
+      <c r="A45" s="43"/>
       <c r="B45" s="10"/>
       <c r="C45" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D45" s="20"/>
-      <c r="E45" s="66"/>
-      <c r="F45" s="61"/>
-      <c r="G45" s="61"/>
-      <c r="H45" s="62"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="33"/>
     </row>
     <row r="46" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A46" s="50"/>
+      <c r="A46" s="43"/>
       <c r="B46" s="10"/>
       <c r="C46" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D46" s="20"/>
-      <c r="E46" s="66"/>
-      <c r="F46" s="61"/>
-      <c r="G46" s="61"/>
-      <c r="H46" s="62"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="33"/>
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A47" s="50"/>
+      <c r="A47" s="43"/>
       <c r="B47" s="10"/>
       <c r="C47" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D47" s="20"/>
-      <c r="E47" s="66"/>
-      <c r="F47" s="61"/>
-      <c r="G47" s="61"/>
-      <c r="H47" s="62"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="33"/>
     </row>
     <row r="48" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A48" s="50"/>
+      <c r="A48" s="43"/>
       <c r="B48" s="10"/>
       <c r="C48" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D48" s="20"/>
-      <c r="E48" s="66"/>
-      <c r="F48" s="61"/>
-      <c r="G48" s="61"/>
-      <c r="H48" s="62"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="33"/>
     </row>
     <row r="49" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A49" s="50"/>
+      <c r="A49" s="43"/>
       <c r="B49" s="10"/>
       <c r="C49" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D49" s="20"/>
-      <c r="E49" s="66"/>
-      <c r="F49" s="61"/>
-      <c r="G49" s="61"/>
-      <c r="H49" s="62"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="33"/>
     </row>
     <row r="50" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A50" s="50"/>
+      <c r="A50" s="43"/>
       <c r="B50" s="10"/>
       <c r="C50" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D50" s="20"/>
-      <c r="E50" s="66"/>
-      <c r="F50" s="61"/>
-      <c r="G50" s="61"/>
-      <c r="H50" s="62"/>
+      <c r="E50" s="31"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="33"/>
     </row>
     <row r="51" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A51" s="50"/>
+      <c r="A51" s="43"/>
       <c r="B51" s="10"/>
       <c r="C51" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D51" s="20"/>
-      <c r="E51" s="66"/>
-      <c r="F51" s="61"/>
-      <c r="G51" s="61"/>
-      <c r="H51" s="62"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="33"/>
     </row>
     <row r="52" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A52" s="51"/>
+      <c r="A52" s="43"/>
       <c r="B52" s="10"/>
+      <c r="C52" s="9" t="s">
+        <v>17</v>
+      </c>
       <c r="D52" s="20"/>
-      <c r="E52" s="66"/>
-      <c r="F52" s="61"/>
-      <c r="G52" s="61"/>
-      <c r="H52" s="62"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="33"/>
     </row>
     <row r="53" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A53" s="52" t="s">
-        <v>15</v>
-      </c>
+      <c r="A53" s="43"/>
       <c r="B53" s="10"/>
       <c r="C53" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D53" s="20"/>
+      <c r="E53" s="31"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="33"/>
+    </row>
+    <row r="54" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A54" s="44"/>
+      <c r="B54" s="10"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="31"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="33"/>
+    </row>
+    <row r="55" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A55" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" s="10"/>
+      <c r="C55" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D53" s="20"/>
-      <c r="E53" s="66"/>
-      <c r="F53" s="61"/>
-      <c r="G53" s="61"/>
-      <c r="H53" s="62"/>
-    </row>
-    <row r="54" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A54" s="52"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" s="21"/>
-      <c r="E54" s="66"/>
-      <c r="F54" s="61"/>
-      <c r="G54" s="61"/>
-      <c r="H54" s="62"/>
-    </row>
-    <row r="55" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A55" s="52"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D55" s="21"/>
-      <c r="E55" s="66"/>
-      <c r="F55" s="61"/>
-      <c r="G55" s="61"/>
-      <c r="H55" s="62"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="33"/>
     </row>
     <row r="56" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A56" s="52"/>
+      <c r="A56" s="45"/>
       <c r="B56" s="8"/>
       <c r="C56" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" s="21"/>
+      <c r="E56" s="31"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="33"/>
+    </row>
+    <row r="57" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A57" s="45"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57" s="21"/>
+      <c r="E57" s="31"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="33"/>
+    </row>
+    <row r="58" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A58" s="45"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D56" s="21"/>
-      <c r="E56" s="66"/>
-      <c r="F56" s="61"/>
-      <c r="G56" s="61"/>
-      <c r="H56" s="62"/>
-    </row>
-    <row r="57" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A57" s="52"/>
-      <c r="B57" s="8"/>
-      <c r="D57" s="21"/>
-      <c r="E57" s="61"/>
-      <c r="F57" s="61"/>
-      <c r="G57" s="61"/>
-      <c r="H57" s="62"/>
-    </row>
-    <row r="58" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A58" s="53"/>
-      <c r="B58" s="7"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="61"/>
-      <c r="F58" s="61"/>
-      <c r="G58" s="61"/>
-      <c r="H58" s="62"/>
-    </row>
-    <row r="59" spans="1:8" ht="9" customHeight="1">
-      <c r="A59" s="53"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="61"/>
-      <c r="F59" s="61"/>
-      <c r="G59" s="61"/>
-      <c r="H59" s="62"/>
-    </row>
-    <row r="60" spans="1:8" ht="9" customHeight="1">
-      <c r="A60" s="53"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="31"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="33"/>
+    </row>
+    <row r="59" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A59" s="45"/>
+      <c r="B59" s="8"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="32"/>
+      <c r="F59" s="32"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="33"/>
+    </row>
+    <row r="60" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
+      <c r="A60" s="46"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="7"/>
       <c r="D60" s="22"/>
-      <c r="E60" s="61"/>
-      <c r="F60" s="61"/>
-      <c r="G60" s="61"/>
-      <c r="H60" s="62"/>
+      <c r="E60" s="32"/>
+      <c r="F60" s="32"/>
+      <c r="G60" s="32"/>
+      <c r="H60" s="33"/>
     </row>
     <row r="61" spans="1:8" ht="9" customHeight="1">
-      <c r="A61" s="53"/>
+      <c r="A61" s="46"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
-      <c r="D61" s="23"/>
-      <c r="E61" s="61"/>
-      <c r="F61" s="61"/>
-      <c r="G61" s="61"/>
-      <c r="H61" s="62"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="32"/>
+      <c r="G61" s="32"/>
+      <c r="H61" s="33"/>
     </row>
     <row r="62" spans="1:8" ht="9" customHeight="1">
-      <c r="A62" s="53"/>
+      <c r="A62" s="46"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
-      <c r="D62" s="23"/>
-      <c r="E62" s="61"/>
-      <c r="F62" s="61"/>
-      <c r="G62" s="61"/>
-      <c r="H62" s="62"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="32"/>
+      <c r="F62" s="32"/>
+      <c r="G62" s="32"/>
+      <c r="H62" s="33"/>
     </row>
     <row r="63" spans="1:8" ht="9" customHeight="1">
-      <c r="A63" s="53"/>
+      <c r="A63" s="46"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
       <c r="D63" s="23"/>
-      <c r="E63" s="61"/>
-      <c r="F63" s="61"/>
-      <c r="G63" s="61"/>
-      <c r="H63" s="62"/>
+      <c r="E63" s="32"/>
+      <c r="F63" s="32"/>
+      <c r="G63" s="32"/>
+      <c r="H63" s="33"/>
     </row>
     <row r="64" spans="1:8" ht="9" customHeight="1">
-      <c r="A64" s="54"/>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
+      <c r="A64" s="46"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
       <c r="D64" s="23"/>
-      <c r="E64" s="61"/>
-      <c r="F64" s="61"/>
-      <c r="G64" s="61"/>
-      <c r="H64" s="62"/>
+      <c r="E64" s="32"/>
+      <c r="F64" s="32"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="33"/>
     </row>
     <row r="65" spans="1:8" ht="9" customHeight="1">
-      <c r="A65" s="78" t="s">
+      <c r="A65" s="46"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="23"/>
+      <c r="E65" s="32"/>
+      <c r="F65" s="32"/>
+      <c r="G65" s="32"/>
+      <c r="H65" s="33"/>
+    </row>
+    <row r="66" spans="1:8" ht="9" customHeight="1">
+      <c r="A66" s="47"/>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="23"/>
+      <c r="E66" s="32"/>
+      <c r="F66" s="32"/>
+      <c r="G66" s="32"/>
+      <c r="H66" s="33"/>
+    </row>
+    <row r="67" spans="1:8" ht="9" customHeight="1">
+      <c r="A67" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="B65" s="79"/>
-      <c r="C65" s="79"/>
-      <c r="D65" s="63" t="s">
+      <c r="B67" s="70"/>
+      <c r="C67" s="70"/>
+      <c r="D67" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="E65" s="63"/>
-      <c r="F65" s="63"/>
-      <c r="G65" s="63"/>
-      <c r="H65" s="64"/>
-    </row>
-    <row r="66" spans="1:8" ht="9" customHeight="1">
-      <c r="A66" s="78"/>
-      <c r="B66" s="79"/>
-      <c r="C66" s="79"/>
-      <c r="D66" s="63" t="s">
-        <v>8</v>
-      </c>
-      <c r="E66" s="63"/>
-      <c r="F66" s="63"/>
-      <c r="G66" s="65"/>
-      <c r="H66" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="9" customHeight="1">
-      <c r="A67" s="78"/>
-      <c r="B67" s="79"/>
-      <c r="C67" s="79"/>
-      <c r="D67" s="55"/>
       <c r="E67" s="56"/>
       <c r="F67" s="56"/>
-      <c r="G67" s="57"/>
-      <c r="H67" s="2"/>
+      <c r="G67" s="56"/>
+      <c r="H67" s="57"/>
     </row>
     <row r="68" spans="1:8" ht="9" customHeight="1">
-      <c r="A68" s="78"/>
-      <c r="B68" s="79"/>
-      <c r="C68" s="79"/>
-      <c r="D68" s="55"/>
+      <c r="A68" s="69"/>
+      <c r="B68" s="70"/>
+      <c r="C68" s="70"/>
+      <c r="D68" s="56" t="s">
+        <v>8</v>
+      </c>
       <c r="E68" s="56"/>
       <c r="F68" s="56"/>
-      <c r="G68" s="57"/>
-      <c r="H68" s="2"/>
+      <c r="G68" s="58"/>
+      <c r="H68" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="69" spans="1:8" ht="9" customHeight="1">
-      <c r="A69" s="78"/>
-      <c r="B69" s="79"/>
-      <c r="C69" s="79"/>
-      <c r="D69" s="55"/>
-      <c r="E69" s="56"/>
-      <c r="F69" s="56"/>
-      <c r="G69" s="57"/>
+      <c r="A69" s="69"/>
+      <c r="B69" s="70"/>
+      <c r="C69" s="70"/>
+      <c r="D69" s="48"/>
+      <c r="E69" s="49"/>
+      <c r="F69" s="49"/>
+      <c r="G69" s="50"/>
       <c r="H69" s="2"/>
     </row>
     <row r="70" spans="1:8" ht="9" customHeight="1">
-      <c r="A70" s="78"/>
-      <c r="B70" s="79"/>
-      <c r="C70" s="79"/>
-      <c r="D70" s="58"/>
-      <c r="E70" s="59"/>
-      <c r="F70" s="59"/>
-      <c r="G70" s="57"/>
+      <c r="A70" s="69"/>
+      <c r="B70" s="70"/>
+      <c r="C70" s="70"/>
+      <c r="D70" s="48"/>
+      <c r="E70" s="49"/>
+      <c r="F70" s="49"/>
+      <c r="G70" s="50"/>
       <c r="H70" s="2"/>
     </row>
     <row r="71" spans="1:8" ht="9" customHeight="1">
-      <c r="A71" s="78"/>
-      <c r="B71" s="79"/>
-      <c r="C71" s="79"/>
-      <c r="D71" s="42" t="s">
+      <c r="A71" s="69"/>
+      <c r="B71" s="70"/>
+      <c r="C71" s="70"/>
+      <c r="D71" s="48"/>
+      <c r="E71" s="49"/>
+      <c r="F71" s="49"/>
+      <c r="G71" s="50"/>
+      <c r="H71" s="2"/>
+    </row>
+    <row r="72" spans="1:8" ht="9" customHeight="1">
+      <c r="A72" s="69"/>
+      <c r="B72" s="70"/>
+      <c r="C72" s="70"/>
+      <c r="D72" s="51"/>
+      <c r="E72" s="52"/>
+      <c r="F72" s="52"/>
+      <c r="G72" s="50"/>
+      <c r="H72" s="2"/>
+    </row>
+    <row r="73" spans="1:8" ht="9" customHeight="1">
+      <c r="A73" s="69"/>
+      <c r="B73" s="70"/>
+      <c r="C73" s="70"/>
+      <c r="D73" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="E71" s="43"/>
-      <c r="F71" s="44"/>
-      <c r="G71" s="28"/>
-      <c r="H71" s="29"/>
-    </row>
-    <row r="72" spans="1:8" ht="9" customHeight="1">
-      <c r="A72" s="78"/>
-      <c r="B72" s="79"/>
-      <c r="C72" s="79"/>
-      <c r="D72" s="34" t="s">
+      <c r="E73" s="80"/>
+      <c r="F73" s="81"/>
+      <c r="G73" s="63"/>
+      <c r="H73" s="64"/>
+    </row>
+    <row r="74" spans="1:8" ht="9" customHeight="1">
+      <c r="A74" s="69"/>
+      <c r="B74" s="70"/>
+      <c r="C74" s="70"/>
+      <c r="D74" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="E72" s="35"/>
-      <c r="F72" s="36"/>
-      <c r="G72" s="30"/>
-      <c r="H72" s="31"/>
-    </row>
-    <row r="73" spans="1:8" ht="9" customHeight="1">
-      <c r="A73" s="78"/>
-      <c r="B73" s="79"/>
-      <c r="C73" s="79"/>
-      <c r="D73" s="60" t="s">
+      <c r="E74" s="74"/>
+      <c r="F74" s="75"/>
+      <c r="G74" s="65"/>
+      <c r="H74" s="66"/>
+    </row>
+    <row r="75" spans="1:8" ht="9" customHeight="1">
+      <c r="A75" s="69"/>
+      <c r="B75" s="70"/>
+      <c r="C75" s="70"/>
+      <c r="D75" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="E73" s="37"/>
-      <c r="F73" s="38"/>
-      <c r="G73" s="28"/>
-      <c r="H73" s="29"/>
-    </row>
-    <row r="74" spans="1:8" ht="9" customHeight="1">
-      <c r="A74" s="78"/>
-      <c r="B74" s="79"/>
-      <c r="C74" s="79"/>
-      <c r="D74" s="34" t="s">
+      <c r="E75" s="54"/>
+      <c r="F75" s="55"/>
+      <c r="G75" s="63"/>
+      <c r="H75" s="64"/>
+    </row>
+    <row r="76" spans="1:8" ht="9" customHeight="1">
+      <c r="A76" s="69"/>
+      <c r="B76" s="70"/>
+      <c r="C76" s="70"/>
+      <c r="D76" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="E74" s="35"/>
-      <c r="F74" s="36"/>
-      <c r="G74" s="30"/>
-      <c r="H74" s="31"/>
-    </row>
-    <row r="75" spans="1:8" ht="9" customHeight="1">
-      <c r="A75" s="78"/>
-      <c r="B75" s="79"/>
-      <c r="C75" s="79"/>
-      <c r="D75" s="37" t="s">
+      <c r="E76" s="74"/>
+      <c r="F76" s="75"/>
+      <c r="G76" s="65"/>
+      <c r="H76" s="66"/>
+    </row>
+    <row r="77" spans="1:8" ht="9" customHeight="1">
+      <c r="A77" s="69"/>
+      <c r="B77" s="70"/>
+      <c r="C77" s="70"/>
+      <c r="D77" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="E75" s="37"/>
-      <c r="F75" s="38"/>
-      <c r="G75" s="28"/>
-      <c r="H75" s="29"/>
-    </row>
-    <row r="76" spans="1:8" ht="9" customHeight="1" thickBot="1">
-      <c r="A76" s="80"/>
-      <c r="B76" s="81"/>
-      <c r="C76" s="81"/>
-      <c r="D76" s="39" t="s">
+      <c r="E77" s="54"/>
+      <c r="F77" s="55"/>
+      <c r="G77" s="63"/>
+      <c r="H77" s="64"/>
+    </row>
+    <row r="78" spans="1:8" ht="9" customHeight="1" thickBot="1">
+      <c r="A78" s="71"/>
+      <c r="B78" s="72"/>
+      <c r="C78" s="72"/>
+      <c r="D78" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="E76" s="40"/>
-      <c r="F76" s="41"/>
-      <c r="G76" s="32"/>
-      <c r="H76" s="33"/>
-    </row>
-    <row r="77" spans="1:8" ht="9" customHeight="1" thickTop="1">
-      <c r="F77" s="45" t="s">
+      <c r="E78" s="77"/>
+      <c r="F78" s="78"/>
+      <c r="G78" s="67"/>
+      <c r="H78" s="68"/>
+    </row>
+    <row r="79" spans="1:8" ht="9" customHeight="1" thickTop="1">
+      <c r="F79" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="G77" s="45"/>
-      <c r="H77" s="45"/>
-    </row>
-    <row r="78" spans="1:8" ht="9" customHeight="1">
-      <c r="A78"/>
-      <c r="B78"/>
-      <c r="C78"/>
-      <c r="D78"/>
-      <c r="E78"/>
-      <c r="F78"/>
-      <c r="G78"/>
-      <c r="H78"/>
-    </row>
-    <row r="79" spans="1:8">
-      <c r="A79"/>
-      <c r="B79"/>
-      <c r="C79"/>
-      <c r="D79"/>
-      <c r="E79"/>
-      <c r="F79"/>
-      <c r="G79"/>
-      <c r="H79"/>
-    </row>
-    <row r="80" spans="1:8">
+      <c r="G79" s="38"/>
+      <c r="H79" s="38"/>
+    </row>
+    <row r="80" spans="1:8" ht="9" customHeight="1">
       <c r="A80"/>
       <c r="B80"/>
       <c r="C80"/>
@@ -2331,65 +2361,114 @@
       <c r="G80"/>
       <c r="H80"/>
     </row>
-    <row r="81" customFormat="1"/>
-    <row r="82" customFormat="1"/>
-    <row r="83" customFormat="1"/>
-    <row r="84" customFormat="1"/>
-    <row r="85" customFormat="1"/>
+    <row r="81" spans="1:8">
+      <c r="A81"/>
+      <c r="B81"/>
+      <c r="C81"/>
+      <c r="D81"/>
+      <c r="E81"/>
+      <c r="F81"/>
+      <c r="G81"/>
+      <c r="H81"/>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82"/>
+      <c r="B82"/>
+      <c r="C82"/>
+      <c r="D82"/>
+      <c r="E82"/>
+      <c r="F82"/>
+      <c r="G82"/>
+      <c r="H82"/>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83"/>
+      <c r="B83"/>
+      <c r="C83"/>
+      <c r="D83"/>
+      <c r="E83"/>
+      <c r="F83"/>
+      <c r="G83"/>
+      <c r="H83"/>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84"/>
+      <c r="B84"/>
+      <c r="C84"/>
+      <c r="D84"/>
+      <c r="E84"/>
+      <c r="F84"/>
+      <c r="G84"/>
+      <c r="H84"/>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85"/>
+      <c r="B85"/>
+      <c r="C85"/>
+      <c r="D85"/>
+      <c r="E85"/>
+      <c r="F85"/>
+      <c r="G85"/>
+      <c r="H85"/>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86"/>
+      <c r="B86"/>
+      <c r="C86"/>
+      <c r="D86"/>
+      <c r="E86"/>
+      <c r="F86"/>
+      <c r="G86"/>
+      <c r="H86"/>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87"/>
+      <c r="B87"/>
+      <c r="C87"/>
+      <c r="D87"/>
+      <c r="E87"/>
+      <c r="F87"/>
+      <c r="G87"/>
+      <c r="H87"/>
+    </row>
   </sheetData>
-  <mergeCells count="92">
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:H38"/>
+  <mergeCells count="96">
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="G73:H74"/>
+    <mergeCell ref="G75:H76"/>
+    <mergeCell ref="G77:H78"/>
+    <mergeCell ref="A67:C78"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="E59:H59"/>
     <mergeCell ref="E60:H60"/>
     <mergeCell ref="E61:H61"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A23"/>
+    <mergeCell ref="A24:A32"/>
+    <mergeCell ref="A33:A37"/>
+    <mergeCell ref="A38:A54"/>
+    <mergeCell ref="A55:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="D71:G71"/>
+    <mergeCell ref="D72:G72"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="D67:H67"/>
+    <mergeCell ref="D68:G68"/>
+    <mergeCell ref="D69:G69"/>
+    <mergeCell ref="D70:G70"/>
     <mergeCell ref="E62:H62"/>
     <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="E65:H65"/>
     <mergeCell ref="E46:H46"/>
     <mergeCell ref="E47:H47"/>
     <mergeCell ref="E48:H48"/>
@@ -2398,38 +2477,58 @@
     <mergeCell ref="E51:H51"/>
     <mergeCell ref="E52:H52"/>
     <mergeCell ref="E53:H53"/>
-    <mergeCell ref="F77:H77"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A21"/>
-    <mergeCell ref="A22:A30"/>
-    <mergeCell ref="A31:A35"/>
-    <mergeCell ref="A36:A52"/>
-    <mergeCell ref="A53:A57"/>
-    <mergeCell ref="A58:A64"/>
-    <mergeCell ref="D69:G69"/>
-    <mergeCell ref="D70:G70"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="D65:H65"/>
-    <mergeCell ref="D66:G66"/>
-    <mergeCell ref="D67:G67"/>
-    <mergeCell ref="D68:G68"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="G71:H72"/>
-    <mergeCell ref="G73:H74"/>
-    <mergeCell ref="G75:H76"/>
-    <mergeCell ref="A65:C76"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D72:F72"/>
     <mergeCell ref="E54:H54"/>
     <mergeCell ref="E55:H55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.195138888888889" bottom="0" header="0" footer="0"/>

--- a/public/assets/templates/maintenance/utility.xlsx
+++ b/public/assets/templates/maintenance/utility.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFC1418-E339-47D8-ADF6-7537737A7657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0094BA53-0B41-4A87-9051-73527FA70E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{FF133B37-4395-463D-9E0A-8A8115D83F24}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="83">
   <si>
     <t>FRM/EUT/01/009/003-02</t>
   </si>
@@ -274,6 +274,9 @@
   </si>
   <si>
     <t xml:space="preserve">: </t>
+  </si>
+  <si>
+    <t>MID</t>
   </si>
 </sst>
 </file>
@@ -370,7 +373,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -599,19 +602,6 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="thin">
         <color auto="1"/>
@@ -767,7 +757,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -780,7 +770,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -825,7 +815,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -840,12 +830,147 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -858,161 +983,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1396,28 +1374,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickTop="1">
-      <c r="A1" s="59"/>
-      <c r="B1" s="60"/>
-      <c r="C1" s="24" t="s">
+      <c r="A1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="69" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="25"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="70"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="61"/>
-      <c r="B2" s="62"/>
-      <c r="C2" s="26" t="s">
+      <c r="A2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="71" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="27"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:8" ht="10" customHeight="1">
       <c r="A3" s="19" t="s">
@@ -1427,15 +1405,15 @@
         <v>71</v>
       </c>
       <c r="C3" s="18"/>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="E3" s="28"/>
-      <c r="F3" s="29" t="s">
+      <c r="E3" s="73"/>
+      <c r="F3" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="29"/>
-      <c r="H3" s="30"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:8" ht="10" customHeight="1">
       <c r="A4" s="19" t="s">
@@ -1445,15 +1423,15 @@
         <v>71</v>
       </c>
       <c r="C4" s="18"/>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="E4" s="28"/>
-      <c r="F4" s="29" t="s">
+      <c r="E4" s="73"/>
+      <c r="F4" s="74" t="s">
         <v>81</v>
       </c>
-      <c r="G4" s="29"/>
-      <c r="H4" s="30"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="75"/>
     </row>
     <row r="5" spans="1:8" ht="10" customHeight="1">
       <c r="A5" s="19" t="s">
@@ -1463,15 +1441,15 @@
         <v>71</v>
       </c>
       <c r="C5" s="18"/>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="73" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="29" t="s">
+      <c r="E5" s="73"/>
+      <c r="F5" s="74" t="s">
         <v>81</v>
       </c>
-      <c r="G5" s="29"/>
-      <c r="H5" s="30"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="75"/>
     </row>
     <row r="6" spans="1:8" ht="10" customHeight="1">
       <c r="A6" s="19" t="s">
@@ -1481,36 +1459,36 @@
         <v>71</v>
       </c>
       <c r="C6" s="18"/>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="29" t="s">
+      <c r="E6" s="73"/>
+      <c r="F6" s="74" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="30"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="75"/>
     </row>
     <row r="7" spans="1:8" s="15" customFormat="1" ht="11" customHeight="1">
       <c r="A7" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="34"/>
+      <c r="C7" s="65"/>
       <c r="D7" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="37"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="68"/>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="53" t="s">
         <v>64</v>
       </c>
       <c r="B8" s="10"/>
@@ -1518,46 +1496,46 @@
         <v>63</v>
       </c>
       <c r="D8" s="20"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="33"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="51"/>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A9" s="39"/>
+      <c r="A9" s="53"/>
       <c r="B9" s="10"/>
       <c r="C9" s="12" t="s">
         <v>62</v>
       </c>
       <c r="D9" s="20"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="33"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="51"/>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A10" s="39"/>
+      <c r="A10" s="53"/>
       <c r="B10" s="10"/>
       <c r="C10" s="12" t="s">
         <v>61</v>
       </c>
       <c r="D10" s="20"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="33"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="50"/>
+      <c r="H10" s="51"/>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A11" s="39"/>
+      <c r="A11" s="53"/>
       <c r="B11" s="10"/>
       <c r="D11" s="20"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="33"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="51"/>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="54" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="10"/>
@@ -1565,145 +1543,145 @@
         <v>59</v>
       </c>
       <c r="D12" s="20"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="33"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="51"/>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A13" s="40"/>
+      <c r="A13" s="54"/>
       <c r="B13" s="10"/>
       <c r="C13" s="12" t="s">
         <v>58</v>
       </c>
       <c r="D13" s="20"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="33"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="51"/>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A14" s="40"/>
+      <c r="A14" s="54"/>
       <c r="B14" s="10"/>
       <c r="C14" s="12" t="s">
         <v>57</v>
       </c>
       <c r="D14" s="20"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="33"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="51"/>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A15" s="40"/>
+      <c r="A15" s="54"/>
       <c r="B15" s="10"/>
       <c r="C15" s="12" t="s">
         <v>56</v>
       </c>
       <c r="D15" s="20"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="33"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="51"/>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A16" s="40"/>
+      <c r="A16" s="54"/>
       <c r="B16" s="10"/>
       <c r="C16" s="12" t="s">
         <v>55</v>
       </c>
       <c r="D16" s="20"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="33"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="51"/>
     </row>
     <row r="17" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A17" s="40"/>
+      <c r="A17" s="54"/>
       <c r="B17" s="10"/>
       <c r="C17" s="12" t="s">
         <v>54</v>
       </c>
       <c r="D17" s="20"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="33"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="51"/>
     </row>
     <row r="18" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A18" s="40"/>
+      <c r="A18" s="54"/>
       <c r="B18" s="10"/>
       <c r="C18" s="12" t="s">
         <v>53</v>
       </c>
       <c r="D18" s="20"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="33"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="51"/>
     </row>
     <row r="19" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A19" s="40"/>
+      <c r="A19" s="54"/>
       <c r="B19" s="10"/>
       <c r="C19" s="12" t="s">
         <v>52</v>
       </c>
       <c r="D19" s="20"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="33"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="51"/>
       <c r="J19" s="6" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A20" s="40"/>
+      <c r="A20" s="54"/>
       <c r="B20" s="10"/>
       <c r="C20" s="12" t="s">
         <v>50</v>
       </c>
       <c r="D20" s="20"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="33"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="51"/>
     </row>
     <row r="21" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A21" s="40"/>
+      <c r="A21" s="54"/>
       <c r="B21" s="10"/>
       <c r="C21" s="14" t="s">
         <v>49</v>
       </c>
       <c r="D21" s="20"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="33"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="51"/>
     </row>
     <row r="22" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A22" s="40"/>
+      <c r="A22" s="54"/>
       <c r="B22" s="10"/>
       <c r="C22" s="14" t="s">
         <v>48</v>
       </c>
       <c r="D22" s="20"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="33"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="51"/>
     </row>
     <row r="23" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A23" s="40"/>
+      <c r="A23" s="54"/>
       <c r="B23" s="10"/>
       <c r="D23" s="20"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="33"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="51"/>
     </row>
     <row r="24" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A24" s="41" t="s">
+      <c r="A24" s="55" t="s">
         <v>47</v>
       </c>
       <c r="B24" s="10"/>
@@ -1711,110 +1689,110 @@
         <v>46</v>
       </c>
       <c r="D24" s="20"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="33"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="51"/>
       <c r="J24" s="13"/>
     </row>
     <row r="25" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A25" s="41"/>
+      <c r="A25" s="55"/>
       <c r="B25" s="10"/>
       <c r="C25" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D25" s="20"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="33"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="51"/>
     </row>
     <row r="26" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A26" s="41"/>
+      <c r="A26" s="55"/>
       <c r="B26" s="10"/>
       <c r="C26" s="12" t="s">
         <v>44</v>
       </c>
       <c r="D26" s="20"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="33"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="51"/>
     </row>
     <row r="27" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A27" s="41"/>
+      <c r="A27" s="55"/>
       <c r="B27" s="10"/>
       <c r="C27" s="12" t="s">
         <v>43</v>
       </c>
       <c r="D27" s="20"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="33"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="51"/>
     </row>
     <row r="28" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A28" s="41"/>
+      <c r="A28" s="55"/>
       <c r="B28" s="10"/>
       <c r="C28" s="12" t="s">
         <v>42</v>
       </c>
       <c r="D28" s="20"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="33"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="50"/>
+      <c r="H28" s="51"/>
     </row>
     <row r="29" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A29" s="41"/>
+      <c r="A29" s="55"/>
       <c r="B29" s="10"/>
       <c r="C29" s="12" t="s">
         <v>41</v>
       </c>
       <c r="D29" s="20"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="33"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="51"/>
     </row>
     <row r="30" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A30" s="41"/>
+      <c r="A30" s="55"/>
       <c r="B30" s="10"/>
       <c r="C30" s="12" t="s">
         <v>40</v>
       </c>
       <c r="D30" s="20"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="33"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="50"/>
+      <c r="G30" s="50"/>
+      <c r="H30" s="51"/>
     </row>
     <row r="31" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A31" s="41"/>
+      <c r="A31" s="55"/>
       <c r="B31" s="10"/>
       <c r="C31" s="12" t="s">
         <v>39</v>
       </c>
       <c r="D31" s="20"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="33"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="50"/>
+      <c r="H31" s="51"/>
     </row>
     <row r="32" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A32" s="41"/>
+      <c r="A32" s="55"/>
       <c r="B32" s="10"/>
       <c r="C32" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D32" s="20"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="33"/>
+      <c r="E32" s="49"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="51"/>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A33" s="41" t="s">
+      <c r="A33" s="55" t="s">
         <v>37</v>
       </c>
       <c r="B33" s="10"/>
@@ -1822,58 +1800,58 @@
         <v>36</v>
       </c>
       <c r="D33" s="20"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="33"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="51"/>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A34" s="41"/>
+      <c r="A34" s="55"/>
       <c r="B34" s="10"/>
       <c r="C34" s="11" t="s">
         <v>35</v>
       </c>
       <c r="D34" s="20"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="33"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="50"/>
+      <c r="G34" s="50"/>
+      <c r="H34" s="51"/>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A35" s="41"/>
+      <c r="A35" s="55"/>
       <c r="B35" s="8"/>
       <c r="C35" s="11" t="s">
         <v>34</v>
       </c>
       <c r="D35" s="21"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="33"/>
+      <c r="E35" s="49"/>
+      <c r="F35" s="50"/>
+      <c r="G35" s="50"/>
+      <c r="H35" s="51"/>
     </row>
     <row r="36" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A36" s="41"/>
+      <c r="A36" s="55"/>
       <c r="B36" s="8"/>
       <c r="C36" s="11" t="s">
         <v>33</v>
       </c>
       <c r="D36" s="21"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="33"/>
+      <c r="E36" s="49"/>
+      <c r="F36" s="50"/>
+      <c r="G36" s="50"/>
+      <c r="H36" s="51"/>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A37" s="41"/>
+      <c r="A37" s="55"/>
       <c r="B37" s="8"/>
       <c r="D37" s="21"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="33"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="50"/>
+      <c r="G37" s="50"/>
+      <c r="H37" s="51"/>
     </row>
     <row r="38" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A38" s="42" t="s">
+      <c r="A38" s="56" t="s">
         <v>32</v>
       </c>
       <c r="B38" s="10"/>
@@ -1881,202 +1859,202 @@
         <v>31</v>
       </c>
       <c r="D38" s="20"/>
-      <c r="E38" s="31"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="33"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="50"/>
+      <c r="G38" s="50"/>
+      <c r="H38" s="51"/>
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A39" s="43"/>
+      <c r="A39" s="57"/>
       <c r="B39" s="10"/>
       <c r="C39" s="9" t="s">
         <v>30</v>
       </c>
       <c r="D39" s="20"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="33"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="50"/>
+      <c r="G39" s="50"/>
+      <c r="H39" s="51"/>
     </row>
     <row r="40" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A40" s="43"/>
+      <c r="A40" s="57"/>
       <c r="B40" s="10"/>
       <c r="C40" s="9" t="s">
         <v>29</v>
       </c>
       <c r="D40" s="20"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="33"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="50"/>
+      <c r="G40" s="50"/>
+      <c r="H40" s="51"/>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A41" s="43"/>
+      <c r="A41" s="57"/>
       <c r="B41" s="10"/>
       <c r="C41" s="9" t="s">
         <v>28</v>
       </c>
       <c r="D41" s="20"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="33"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="50"/>
+      <c r="G41" s="50"/>
+      <c r="H41" s="51"/>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A42" s="43"/>
+      <c r="A42" s="57"/>
       <c r="B42" s="10"/>
       <c r="C42" s="9" t="s">
         <v>27</v>
       </c>
       <c r="D42" s="20"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="33"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="50"/>
+      <c r="G42" s="50"/>
+      <c r="H42" s="51"/>
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A43" s="43"/>
+      <c r="A43" s="57"/>
       <c r="B43" s="10"/>
       <c r="C43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="D43" s="20"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="33"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="50"/>
+      <c r="G43" s="50"/>
+      <c r="H43" s="51"/>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A44" s="43"/>
+      <c r="A44" s="57"/>
       <c r="B44" s="10"/>
       <c r="C44" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D44" s="20"/>
-      <c r="E44" s="31"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="33"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="50"/>
+      <c r="G44" s="50"/>
+      <c r="H44" s="51"/>
     </row>
     <row r="45" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A45" s="43"/>
+      <c r="A45" s="57"/>
       <c r="B45" s="10"/>
       <c r="C45" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D45" s="20"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="33"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="50"/>
+      <c r="G45" s="50"/>
+      <c r="H45" s="51"/>
     </row>
     <row r="46" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A46" s="43"/>
+      <c r="A46" s="57"/>
       <c r="B46" s="10"/>
       <c r="C46" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D46" s="20"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="33"/>
+      <c r="E46" s="49"/>
+      <c r="F46" s="50"/>
+      <c r="G46" s="50"/>
+      <c r="H46" s="51"/>
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A47" s="43"/>
+      <c r="A47" s="57"/>
       <c r="B47" s="10"/>
       <c r="C47" s="9" t="s">
         <v>22</v>
       </c>
       <c r="D47" s="20"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="33"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="50"/>
+      <c r="G47" s="50"/>
+      <c r="H47" s="51"/>
     </row>
     <row r="48" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A48" s="43"/>
+      <c r="A48" s="57"/>
       <c r="B48" s="10"/>
       <c r="C48" s="9" t="s">
         <v>21</v>
       </c>
       <c r="D48" s="20"/>
-      <c r="E48" s="31"/>
-      <c r="F48" s="32"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="33"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="50"/>
+      <c r="G48" s="50"/>
+      <c r="H48" s="51"/>
     </row>
     <row r="49" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A49" s="43"/>
+      <c r="A49" s="57"/>
       <c r="B49" s="10"/>
       <c r="C49" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D49" s="20"/>
-      <c r="E49" s="31"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="33"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="50"/>
+      <c r="G49" s="50"/>
+      <c r="H49" s="51"/>
     </row>
     <row r="50" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A50" s="43"/>
+      <c r="A50" s="57"/>
       <c r="B50" s="10"/>
       <c r="C50" s="9" t="s">
         <v>19</v>
       </c>
       <c r="D50" s="20"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="33"/>
+      <c r="E50" s="49"/>
+      <c r="F50" s="50"/>
+      <c r="G50" s="50"/>
+      <c r="H50" s="51"/>
     </row>
     <row r="51" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A51" s="43"/>
+      <c r="A51" s="57"/>
       <c r="B51" s="10"/>
       <c r="C51" s="9" t="s">
         <v>18</v>
       </c>
       <c r="D51" s="20"/>
-      <c r="E51" s="31"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="32"/>
-      <c r="H51" s="33"/>
+      <c r="E51" s="49"/>
+      <c r="F51" s="50"/>
+      <c r="G51" s="50"/>
+      <c r="H51" s="51"/>
     </row>
     <row r="52" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A52" s="43"/>
+      <c r="A52" s="57"/>
       <c r="B52" s="10"/>
       <c r="C52" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D52" s="20"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="32"/>
-      <c r="H52" s="33"/>
+      <c r="E52" s="49"/>
+      <c r="F52" s="50"/>
+      <c r="G52" s="50"/>
+      <c r="H52" s="51"/>
     </row>
     <row r="53" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A53" s="43"/>
+      <c r="A53" s="57"/>
       <c r="B53" s="10"/>
       <c r="C53" s="9" t="s">
         <v>16</v>
       </c>
       <c r="D53" s="20"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
-      <c r="H53" s="33"/>
+      <c r="E53" s="49"/>
+      <c r="F53" s="50"/>
+      <c r="G53" s="50"/>
+      <c r="H53" s="51"/>
     </row>
     <row r="54" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A54" s="44"/>
+      <c r="A54" s="58"/>
       <c r="B54" s="10"/>
       <c r="D54" s="20"/>
-      <c r="E54" s="31"/>
-      <c r="F54" s="32"/>
-      <c r="G54" s="32"/>
-      <c r="H54" s="33"/>
+      <c r="E54" s="49"/>
+      <c r="F54" s="50"/>
+      <c r="G54" s="50"/>
+      <c r="H54" s="51"/>
     </row>
     <row r="55" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A55" s="45" t="s">
+      <c r="A55" s="59" t="s">
         <v>15</v>
       </c>
       <c r="B55" s="10"/>
@@ -2084,272 +2062,274 @@
         <v>14</v>
       </c>
       <c r="D55" s="20"/>
-      <c r="E55" s="31"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="33"/>
+      <c r="E55" s="49"/>
+      <c r="F55" s="50"/>
+      <c r="G55" s="50"/>
+      <c r="H55" s="51"/>
     </row>
     <row r="56" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A56" s="45"/>
+      <c r="A56" s="59"/>
       <c r="B56" s="8"/>
       <c r="C56" s="9" t="s">
         <v>13</v>
       </c>
       <c r="D56" s="21"/>
-      <c r="E56" s="31"/>
-      <c r="F56" s="32"/>
-      <c r="G56" s="32"/>
-      <c r="H56" s="33"/>
+      <c r="E56" s="49"/>
+      <c r="F56" s="50"/>
+      <c r="G56" s="50"/>
+      <c r="H56" s="51"/>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A57" s="45"/>
+      <c r="A57" s="59"/>
       <c r="B57" s="8"/>
       <c r="C57" s="9" t="s">
         <v>12</v>
       </c>
       <c r="D57" s="21"/>
-      <c r="E57" s="31"/>
-      <c r="F57" s="32"/>
-      <c r="G57" s="32"/>
-      <c r="H57" s="33"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="50"/>
+      <c r="G57" s="50"/>
+      <c r="H57" s="51"/>
     </row>
     <row r="58" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A58" s="45"/>
+      <c r="A58" s="59"/>
       <c r="B58" s="8"/>
       <c r="C58" s="9" t="s">
         <v>11</v>
       </c>
       <c r="D58" s="21"/>
-      <c r="E58" s="31"/>
-      <c r="F58" s="32"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="33"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="50"/>
+      <c r="G58" s="50"/>
+      <c r="H58" s="51"/>
     </row>
     <row r="59" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A59" s="45"/>
+      <c r="A59" s="59"/>
       <c r="B59" s="8"/>
       <c r="D59" s="21"/>
-      <c r="E59" s="32"/>
-      <c r="F59" s="32"/>
-      <c r="G59" s="32"/>
-      <c r="H59" s="33"/>
+      <c r="E59" s="50"/>
+      <c r="F59" s="50"/>
+      <c r="G59" s="50"/>
+      <c r="H59" s="51"/>
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A60" s="46"/>
+      <c r="A60" s="60"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
       <c r="D60" s="22"/>
-      <c r="E60" s="32"/>
-      <c r="F60" s="32"/>
-      <c r="G60" s="32"/>
-      <c r="H60" s="33"/>
+      <c r="E60" s="50"/>
+      <c r="F60" s="50"/>
+      <c r="G60" s="50"/>
+      <c r="H60" s="51"/>
     </row>
     <row r="61" spans="1:8" ht="9" customHeight="1">
-      <c r="A61" s="46"/>
+      <c r="A61" s="60"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="22"/>
-      <c r="E61" s="32"/>
-      <c r="F61" s="32"/>
-      <c r="G61" s="32"/>
-      <c r="H61" s="33"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="50"/>
+      <c r="G61" s="50"/>
+      <c r="H61" s="51"/>
     </row>
     <row r="62" spans="1:8" ht="9" customHeight="1">
-      <c r="A62" s="46"/>
+      <c r="A62" s="60"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
       <c r="D62" s="22"/>
-      <c r="E62" s="32"/>
-      <c r="F62" s="32"/>
-      <c r="G62" s="32"/>
-      <c r="H62" s="33"/>
+      <c r="E62" s="50"/>
+      <c r="F62" s="50"/>
+      <c r="G62" s="50"/>
+      <c r="H62" s="51"/>
     </row>
     <row r="63" spans="1:8" ht="9" customHeight="1">
-      <c r="A63" s="46"/>
+      <c r="A63" s="60"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
       <c r="D63" s="23"/>
-      <c r="E63" s="32"/>
-      <c r="F63" s="32"/>
-      <c r="G63" s="32"/>
-      <c r="H63" s="33"/>
+      <c r="E63" s="50"/>
+      <c r="F63" s="50"/>
+      <c r="G63" s="50"/>
+      <c r="H63" s="51"/>
     </row>
     <row r="64" spans="1:8" ht="9" customHeight="1">
-      <c r="A64" s="46"/>
+      <c r="A64" s="60"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
       <c r="D64" s="23"/>
-      <c r="E64" s="32"/>
-      <c r="F64" s="32"/>
-      <c r="G64" s="32"/>
-      <c r="H64" s="33"/>
+      <c r="E64" s="50"/>
+      <c r="F64" s="50"/>
+      <c r="G64" s="50"/>
+      <c r="H64" s="51"/>
     </row>
     <row r="65" spans="1:8" ht="9" customHeight="1">
-      <c r="A65" s="46"/>
+      <c r="A65" s="60"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
       <c r="D65" s="23"/>
-      <c r="E65" s="32"/>
-      <c r="F65" s="32"/>
-      <c r="G65" s="32"/>
-      <c r="H65" s="33"/>
+      <c r="E65" s="50"/>
+      <c r="F65" s="50"/>
+      <c r="G65" s="50"/>
+      <c r="H65" s="51"/>
     </row>
     <row r="66" spans="1:8" ht="9" customHeight="1">
-      <c r="A66" s="47"/>
+      <c r="A66" s="61"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="23"/>
-      <c r="E66" s="32"/>
-      <c r="F66" s="32"/>
-      <c r="G66" s="32"/>
-      <c r="H66" s="33"/>
+      <c r="E66" s="50"/>
+      <c r="F66" s="50"/>
+      <c r="G66" s="50"/>
+      <c r="H66" s="51"/>
     </row>
     <row r="67" spans="1:8" ht="9" customHeight="1">
-      <c r="A67" s="69" t="s">
+      <c r="A67" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="B67" s="70"/>
-      <c r="C67" s="70"/>
-      <c r="D67" s="56" t="s">
+      <c r="B67" s="35"/>
+      <c r="C67" s="35"/>
+      <c r="D67" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="E67" s="56"/>
-      <c r="F67" s="56"/>
-      <c r="G67" s="56"/>
-      <c r="H67" s="57"/>
+      <c r="E67" s="63"/>
+      <c r="F67" s="63"/>
+      <c r="G67" s="63"/>
+      <c r="H67" s="64"/>
     </row>
     <row r="68" spans="1:8" ht="9" customHeight="1">
-      <c r="A68" s="69"/>
-      <c r="B68" s="70"/>
-      <c r="C68" s="70"/>
-      <c r="D68" s="56" t="s">
+      <c r="A68" s="34"/>
+      <c r="B68" s="35"/>
+      <c r="C68" s="35"/>
+      <c r="D68" s="76" t="s">
+        <v>82</v>
+      </c>
+      <c r="E68" s="76"/>
+      <c r="F68" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="E68" s="56"/>
-      <c r="F68" s="56"/>
-      <c r="G68" s="58"/>
+      <c r="G68" s="76"/>
       <c r="H68" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="9" customHeight="1">
-      <c r="A69" s="69"/>
-      <c r="B69" s="70"/>
-      <c r="C69" s="70"/>
-      <c r="D69" s="48"/>
-      <c r="E69" s="49"/>
-      <c r="F69" s="49"/>
-      <c r="G69" s="50"/>
+      <c r="A69" s="34"/>
+      <c r="B69" s="35"/>
+      <c r="C69" s="35"/>
+      <c r="D69" s="77"/>
+      <c r="E69" s="77"/>
+      <c r="F69" s="76"/>
+      <c r="G69" s="76"/>
       <c r="H69" s="2"/>
     </row>
     <row r="70" spans="1:8" ht="9" customHeight="1">
-      <c r="A70" s="69"/>
-      <c r="B70" s="70"/>
-      <c r="C70" s="70"/>
-      <c r="D70" s="48"/>
-      <c r="E70" s="49"/>
-      <c r="F70" s="49"/>
-      <c r="G70" s="50"/>
+      <c r="A70" s="34"/>
+      <c r="B70" s="35"/>
+      <c r="C70" s="35"/>
+      <c r="D70" s="77"/>
+      <c r="E70" s="77"/>
+      <c r="F70" s="76"/>
+      <c r="G70" s="76"/>
       <c r="H70" s="2"/>
     </row>
     <row r="71" spans="1:8" ht="9" customHeight="1">
-      <c r="A71" s="69"/>
-      <c r="B71" s="70"/>
-      <c r="C71" s="70"/>
-      <c r="D71" s="48"/>
-      <c r="E71" s="49"/>
-      <c r="F71" s="49"/>
-      <c r="G71" s="50"/>
+      <c r="A71" s="34"/>
+      <c r="B71" s="35"/>
+      <c r="C71" s="35"/>
+      <c r="D71" s="77"/>
+      <c r="E71" s="77"/>
+      <c r="F71" s="76"/>
+      <c r="G71" s="76"/>
       <c r="H71" s="2"/>
     </row>
     <row r="72" spans="1:8" ht="9" customHeight="1">
-      <c r="A72" s="69"/>
-      <c r="B72" s="70"/>
-      <c r="C72" s="70"/>
-      <c r="D72" s="51"/>
-      <c r="E72" s="52"/>
-      <c r="F72" s="52"/>
-      <c r="G72" s="50"/>
+      <c r="A72" s="34"/>
+      <c r="B72" s="35"/>
+      <c r="C72" s="35"/>
+      <c r="D72" s="77"/>
+      <c r="E72" s="77"/>
+      <c r="F72" s="76"/>
+      <c r="G72" s="76"/>
       <c r="H72" s="2"/>
     </row>
     <row r="73" spans="1:8" ht="9" customHeight="1">
-      <c r="A73" s="69"/>
-      <c r="B73" s="70"/>
-      <c r="C73" s="70"/>
-      <c r="D73" s="79" t="s">
+      <c r="A73" s="34"/>
+      <c r="B73" s="35"/>
+      <c r="C73" s="35"/>
+      <c r="D73" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E73" s="80"/>
-      <c r="F73" s="81"/>
-      <c r="G73" s="63"/>
-      <c r="H73" s="64"/>
+      <c r="E73" s="47"/>
+      <c r="F73" s="48"/>
+      <c r="G73" s="28"/>
+      <c r="H73" s="29"/>
     </row>
     <row r="74" spans="1:8" ht="9" customHeight="1">
-      <c r="A74" s="69"/>
-      <c r="B74" s="70"/>
-      <c r="C74" s="70"/>
-      <c r="D74" s="73" t="s">
+      <c r="A74" s="34"/>
+      <c r="B74" s="35"/>
+      <c r="C74" s="35"/>
+      <c r="D74" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="E74" s="74"/>
-      <c r="F74" s="75"/>
-      <c r="G74" s="65"/>
-      <c r="H74" s="66"/>
+      <c r="E74" s="39"/>
+      <c r="F74" s="40"/>
+      <c r="G74" s="30"/>
+      <c r="H74" s="31"/>
     </row>
     <row r="75" spans="1:8" ht="9" customHeight="1">
-      <c r="A75" s="69"/>
-      <c r="B75" s="70"/>
-      <c r="C75" s="70"/>
-      <c r="D75" s="53" t="s">
+      <c r="A75" s="34"/>
+      <c r="B75" s="35"/>
+      <c r="C75" s="35"/>
+      <c r="D75" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="E75" s="54"/>
-      <c r="F75" s="55"/>
-      <c r="G75" s="63"/>
-      <c r="H75" s="64"/>
+      <c r="E75" s="41"/>
+      <c r="F75" s="42"/>
+      <c r="G75" s="28"/>
+      <c r="H75" s="29"/>
     </row>
     <row r="76" spans="1:8" ht="9" customHeight="1">
-      <c r="A76" s="69"/>
-      <c r="B76" s="70"/>
-      <c r="C76" s="70"/>
-      <c r="D76" s="73" t="s">
+      <c r="A76" s="34"/>
+      <c r="B76" s="35"/>
+      <c r="C76" s="35"/>
+      <c r="D76" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E76" s="74"/>
-      <c r="F76" s="75"/>
-      <c r="G76" s="65"/>
-      <c r="H76" s="66"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="40"/>
+      <c r="G76" s="30"/>
+      <c r="H76" s="31"/>
     </row>
     <row r="77" spans="1:8" ht="9" customHeight="1">
-      <c r="A77" s="69"/>
-      <c r="B77" s="70"/>
-      <c r="C77" s="70"/>
-      <c r="D77" s="54" t="s">
+      <c r="A77" s="34"/>
+      <c r="B77" s="35"/>
+      <c r="C77" s="35"/>
+      <c r="D77" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="E77" s="54"/>
-      <c r="F77" s="55"/>
-      <c r="G77" s="63"/>
-      <c r="H77" s="64"/>
+      <c r="E77" s="41"/>
+      <c r="F77" s="42"/>
+      <c r="G77" s="28"/>
+      <c r="H77" s="29"/>
     </row>
     <row r="78" spans="1:8" ht="9" customHeight="1" thickBot="1">
-      <c r="A78" s="71"/>
-      <c r="B78" s="72"/>
-      <c r="C78" s="72"/>
-      <c r="D78" s="76" t="s">
+      <c r="A78" s="36"/>
+      <c r="B78" s="37"/>
+      <c r="C78" s="37"/>
+      <c r="D78" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="E78" s="77"/>
-      <c r="F78" s="78"/>
-      <c r="G78" s="67"/>
-      <c r="H78" s="68"/>
+      <c r="E78" s="44"/>
+      <c r="F78" s="45"/>
+      <c r="G78" s="32"/>
+      <c r="H78" s="33"/>
     </row>
     <row r="79" spans="1:8" ht="9" customHeight="1" thickTop="1">
-      <c r="F79" s="38" t="s">
+      <c r="F79" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="G79" s="38"/>
-      <c r="H79" s="38"/>
+      <c r="G79" s="52"/>
+      <c r="H79" s="52"/>
     </row>
     <row r="80" spans="1:8" ht="9" customHeight="1">
       <c r="A80"/>
@@ -2361,78 +2341,100 @@
       <c r="G80"/>
       <c r="H80"/>
     </row>
-    <row r="81" spans="1:8">
-      <c r="A81"/>
-      <c r="B81"/>
-      <c r="C81"/>
-      <c r="D81"/>
-      <c r="E81"/>
-      <c r="F81"/>
-      <c r="G81"/>
-      <c r="H81"/>
-    </row>
-    <row r="82" spans="1:8">
-      <c r="A82"/>
-      <c r="B82"/>
-      <c r="C82"/>
-      <c r="D82"/>
-      <c r="E82"/>
-      <c r="F82"/>
-      <c r="G82"/>
-      <c r="H82"/>
-    </row>
-    <row r="83" spans="1:8">
-      <c r="A83"/>
-      <c r="B83"/>
-      <c r="C83"/>
-      <c r="D83"/>
-      <c r="E83"/>
-      <c r="F83"/>
-      <c r="G83"/>
-      <c r="H83"/>
-    </row>
-    <row r="84" spans="1:8">
-      <c r="A84"/>
-      <c r="B84"/>
-      <c r="C84"/>
-      <c r="D84"/>
-      <c r="E84"/>
-      <c r="F84"/>
-      <c r="G84"/>
-      <c r="H84"/>
-    </row>
-    <row r="85" spans="1:8">
-      <c r="A85"/>
-      <c r="B85"/>
-      <c r="C85"/>
-      <c r="D85"/>
-      <c r="E85"/>
-      <c r="F85"/>
-      <c r="G85"/>
-      <c r="H85"/>
-    </row>
-    <row r="86" spans="1:8">
-      <c r="A86"/>
-      <c r="B86"/>
-      <c r="C86"/>
-      <c r="D86"/>
-      <c r="E86"/>
-      <c r="F86"/>
-      <c r="G86"/>
-      <c r="H86"/>
-    </row>
-    <row r="87" spans="1:8">
-      <c r="A87"/>
-      <c r="B87"/>
-      <c r="C87"/>
-      <c r="D87"/>
-      <c r="E87"/>
-      <c r="F87"/>
-      <c r="G87"/>
-      <c r="H87"/>
-    </row>
+    <row r="81" customFormat="1"/>
+    <row r="82" customFormat="1"/>
+    <row r="83" customFormat="1"/>
+    <row r="84" customFormat="1"/>
+    <row r="85" customFormat="1"/>
+    <row r="86" customFormat="1"/>
+    <row r="87" customFormat="1"/>
   </sheetData>
-  <mergeCells count="96">
+  <mergeCells count="101">
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A23"/>
+    <mergeCell ref="A24:A32"/>
+    <mergeCell ref="A33:A37"/>
+    <mergeCell ref="A38:A54"/>
+    <mergeCell ref="A55:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="D67:H67"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="G73:H74"/>
     <mergeCell ref="G75:H76"/>
@@ -2449,86 +2451,6 @@
     <mergeCell ref="E59:H59"/>
     <mergeCell ref="E60:H60"/>
     <mergeCell ref="E61:H61"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A23"/>
-    <mergeCell ref="A24:A32"/>
-    <mergeCell ref="A33:A37"/>
-    <mergeCell ref="A38:A54"/>
-    <mergeCell ref="A55:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="D71:G71"/>
-    <mergeCell ref="D72:G72"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="D67:H67"/>
-    <mergeCell ref="D68:G68"/>
-    <mergeCell ref="D69:G69"/>
-    <mergeCell ref="D70:G70"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F5:H5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.195138888888889" bottom="0" header="0" footer="0"/>

--- a/public/assets/templates/maintenance/utility.xlsx
+++ b/public/assets/templates/maintenance/utility.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0094BA53-0B41-4A87-9051-73527FA70E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D423C692-D54F-495E-A554-D99A5869F8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{FF133B37-4395-463D-9E0A-8A8115D83F24}"/>
   </bookViews>
@@ -33,18 +33,9 @@
     <t>FRM/EUT/01/009/003-02</t>
   </si>
   <si>
-    <t>Staff User</t>
-  </si>
-  <si>
-    <t>Diterima</t>
-  </si>
-  <si>
     <t>Staff Engineering</t>
   </si>
   <si>
-    <t>Diketahui : Miftah Hasan Fuadi</t>
-  </si>
-  <si>
     <t>Teknisi</t>
   </si>
   <si>
@@ -277,13 +268,22 @@
   </si>
   <si>
     <t>MID</t>
+  </si>
+  <si>
+    <t>Diketahui : Reja Firmansyah</t>
+  </si>
+  <si>
+    <t>Supervisor Engineering</t>
+  </si>
+  <si>
+    <t>Diperiksa : Miftah Hasan Fuadi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,10 +292,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -303,60 +310,60 @@
       <sz val="7"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="7"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="7"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="7"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="7"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -373,7 +380,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -404,26 +411,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="double">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -472,15 +459,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -557,7 +535,138 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
         <color auto="1"/>
       </left>
       <right/>
@@ -566,33 +675,13 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
       <right style="double">
         <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -601,9 +690,13 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="double">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -612,11 +705,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color auto="1"/>
       </left>
-      <right/>
-      <top style="thin">
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="double">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -625,59 +720,7 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="double">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
         <color auto="1"/>
       </left>
       <right style="thin">
@@ -687,314 +730,243 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="double">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="double">
-        <color auto="1"/>
-      </right>
-      <top style="double">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="double">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="double">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{278D0532-A174-4E19-AB55-E5A83F7E300C}"/>
     <cellStyle name="Normal_Inspection Test Plan" xfId="1" xr:uid="{469197BC-B19A-4CFC-9112-6ABFBE5215E5}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1376,891 +1348,891 @@
     <row r="1" spans="1:8" ht="15" thickTop="1">
       <c r="A1" s="24"/>
       <c r="B1" s="25"/>
-      <c r="C1" s="69" t="s">
-        <v>75</v>
-      </c>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="70"/>
+      <c r="C1" s="64" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="65"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="26"/>
       <c r="B2" s="27"/>
-      <c r="C2" s="71" t="s">
-        <v>74</v>
-      </c>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="72"/>
+      <c r="C2" s="66" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="67"/>
     </row>
     <row r="3" spans="1:8" ht="10" customHeight="1">
       <c r="A3" s="19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C3" s="18"/>
-      <c r="D3" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" s="73"/>
-      <c r="F3" s="74" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" s="74"/>
-      <c r="H3" s="75"/>
+      <c r="D3" s="68" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="68"/>
+      <c r="F3" s="69" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="69"/>
+      <c r="H3" s="70"/>
     </row>
     <row r="4" spans="1:8" ht="10" customHeight="1">
       <c r="A4" s="19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C4" s="18"/>
-      <c r="D4" s="73" t="s">
-        <v>79</v>
-      </c>
-      <c r="E4" s="73"/>
-      <c r="F4" s="74" t="s">
-        <v>81</v>
-      </c>
-      <c r="G4" s="74"/>
-      <c r="H4" s="75"/>
+      <c r="D4" s="68" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="68"/>
+      <c r="F4" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="69"/>
+      <c r="H4" s="70"/>
     </row>
     <row r="5" spans="1:8" ht="10" customHeight="1">
       <c r="A5" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="18"/>
+      <c r="D5" s="68" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="68"/>
+      <c r="F5" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="73" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5" s="73"/>
-      <c r="F5" s="74" t="s">
-        <v>81</v>
-      </c>
-      <c r="G5" s="74"/>
-      <c r="H5" s="75"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="70"/>
     </row>
     <row r="6" spans="1:8" ht="10" customHeight="1">
       <c r="A6" s="19" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C6" s="18"/>
-      <c r="D6" s="73" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="73"/>
-      <c r="F6" s="74" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="74"/>
-      <c r="H6" s="75"/>
+      <c r="D6" s="68" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="68"/>
+      <c r="F6" s="69" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6" s="69"/>
+      <c r="H6" s="70"/>
     </row>
     <row r="7" spans="1:8" s="15" customFormat="1" ht="11" customHeight="1">
       <c r="A7" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="65" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="65"/>
+        <v>65</v>
+      </c>
+      <c r="B7" s="60" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="60"/>
       <c r="D7" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="68"/>
+        <v>63</v>
+      </c>
+      <c r="E7" s="61" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="63"/>
     </row>
     <row r="8" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A8" s="53" t="s">
-        <v>64</v>
+      <c r="A8" s="49" t="s">
+        <v>61</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D8" s="20"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="51"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A9" s="53"/>
+      <c r="A9" s="49"/>
       <c r="B9" s="10"/>
       <c r="C9" s="12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D9" s="20"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="51"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="46"/>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A10" s="53"/>
+      <c r="A10" s="49"/>
       <c r="B10" s="10"/>
       <c r="C10" s="12" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D10" s="20"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="51"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="46"/>
     </row>
     <row r="11" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A11" s="53"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="10"/>
       <c r="D11" s="20"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="51"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="46"/>
     </row>
     <row r="12" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A12" s="54" t="s">
-        <v>60</v>
+      <c r="A12" s="50" t="s">
+        <v>57</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="12" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D12" s="20"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="51"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="46"/>
     </row>
     <row r="13" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A13" s="54"/>
+      <c r="A13" s="50"/>
       <c r="B13" s="10"/>
       <c r="C13" s="12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D13" s="20"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="51"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="46"/>
     </row>
     <row r="14" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A14" s="54"/>
+      <c r="A14" s="50"/>
       <c r="B14" s="10"/>
       <c r="C14" s="12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14" s="20"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="51"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="46"/>
     </row>
     <row r="15" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A15" s="54"/>
+      <c r="A15" s="50"/>
       <c r="B15" s="10"/>
       <c r="C15" s="12" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D15" s="20"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="51"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="46"/>
     </row>
     <row r="16" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A16" s="54"/>
+      <c r="A16" s="50"/>
       <c r="B16" s="10"/>
       <c r="C16" s="12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D16" s="20"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="51"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="46"/>
     </row>
     <row r="17" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A17" s="54"/>
+      <c r="A17" s="50"/>
       <c r="B17" s="10"/>
       <c r="C17" s="12" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D17" s="20"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="51"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="46"/>
     </row>
     <row r="18" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A18" s="54"/>
+      <c r="A18" s="50"/>
       <c r="B18" s="10"/>
       <c r="C18" s="12" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D18" s="20"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="51"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="46"/>
     </row>
     <row r="19" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A19" s="54"/>
+      <c r="A19" s="50"/>
       <c r="B19" s="10"/>
       <c r="C19" s="12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D19" s="20"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="51"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="46"/>
       <c r="J19" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A20" s="54"/>
+      <c r="A20" s="50"/>
       <c r="B20" s="10"/>
       <c r="C20" s="12" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D20" s="20"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="51"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="46"/>
     </row>
     <row r="21" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A21" s="54"/>
+      <c r="A21" s="50"/>
       <c r="B21" s="10"/>
       <c r="C21" s="14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D21" s="20"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="51"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="46"/>
     </row>
     <row r="22" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A22" s="54"/>
+      <c r="A22" s="50"/>
       <c r="B22" s="10"/>
       <c r="C22" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D22" s="20"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="51"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="46"/>
     </row>
     <row r="23" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A23" s="54"/>
+      <c r="A23" s="50"/>
       <c r="B23" s="10"/>
       <c r="D23" s="20"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="51"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="46"/>
     </row>
     <row r="24" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A24" s="55" t="s">
-        <v>47</v>
+      <c r="A24" s="51" t="s">
+        <v>44</v>
       </c>
       <c r="B24" s="10"/>
       <c r="C24" s="12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D24" s="20"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="51"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="46"/>
       <c r="J24" s="13"/>
     </row>
     <row r="25" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A25" s="55"/>
+      <c r="A25" s="51"/>
       <c r="B25" s="10"/>
       <c r="C25" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D25" s="20"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="51"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="46"/>
     </row>
     <row r="26" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A26" s="55"/>
+      <c r="A26" s="51"/>
       <c r="B26" s="10"/>
       <c r="C26" s="12" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D26" s="20"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="51"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="46"/>
     </row>
     <row r="27" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A27" s="55"/>
+      <c r="A27" s="51"/>
       <c r="B27" s="10"/>
       <c r="C27" s="12" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D27" s="20"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="51"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="46"/>
     </row>
     <row r="28" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A28" s="55"/>
+      <c r="A28" s="51"/>
       <c r="B28" s="10"/>
       <c r="C28" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D28" s="20"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="51"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="46"/>
     </row>
     <row r="29" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A29" s="55"/>
+      <c r="A29" s="51"/>
       <c r="B29" s="10"/>
       <c r="C29" s="12" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D29" s="20"/>
-      <c r="E29" s="49"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="51"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="46"/>
     </row>
     <row r="30" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A30" s="55"/>
+      <c r="A30" s="51"/>
       <c r="B30" s="10"/>
       <c r="C30" s="12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D30" s="20"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="50"/>
-      <c r="H30" s="51"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="46"/>
     </row>
     <row r="31" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A31" s="55"/>
+      <c r="A31" s="51"/>
       <c r="B31" s="10"/>
       <c r="C31" s="12" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D31" s="20"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="51"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="45"/>
+      <c r="H31" s="46"/>
     </row>
     <row r="32" spans="1:10" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A32" s="55"/>
+      <c r="A32" s="51"/>
       <c r="B32" s="10"/>
       <c r="C32" s="12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D32" s="20"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="51"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="46"/>
     </row>
     <row r="33" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A33" s="55" t="s">
-        <v>37</v>
+      <c r="A33" s="51" t="s">
+        <v>34</v>
       </c>
       <c r="B33" s="10"/>
       <c r="C33" s="11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D33" s="20"/>
-      <c r="E33" s="49"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="51"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="46"/>
     </row>
     <row r="34" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A34" s="55"/>
+      <c r="A34" s="51"/>
       <c r="B34" s="10"/>
       <c r="C34" s="11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D34" s="20"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="51"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="45"/>
+      <c r="H34" s="46"/>
     </row>
     <row r="35" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A35" s="55"/>
+      <c r="A35" s="51"/>
       <c r="B35" s="8"/>
       <c r="C35" s="11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D35" s="21"/>
-      <c r="E35" s="49"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="51"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="45"/>
+      <c r="H35" s="46"/>
     </row>
     <row r="36" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A36" s="55"/>
+      <c r="A36" s="51"/>
       <c r="B36" s="8"/>
       <c r="C36" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D36" s="21"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="51"/>
+      <c r="E36" s="44"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="46"/>
     </row>
     <row r="37" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A37" s="55"/>
+      <c r="A37" s="51"/>
       <c r="B37" s="8"/>
       <c r="D37" s="21"/>
-      <c r="E37" s="49"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="51"/>
+      <c r="E37" s="44"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="46"/>
     </row>
     <row r="38" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A38" s="56" t="s">
-        <v>32</v>
+      <c r="A38" s="52" t="s">
+        <v>29</v>
       </c>
       <c r="B38" s="10"/>
       <c r="C38" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D38" s="20"/>
-      <c r="E38" s="49"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="51"/>
+      <c r="E38" s="44"/>
+      <c r="F38" s="45"/>
+      <c r="G38" s="45"/>
+      <c r="H38" s="46"/>
     </row>
     <row r="39" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A39" s="57"/>
+      <c r="A39" s="53"/>
       <c r="B39" s="10"/>
       <c r="C39" s="9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D39" s="20"/>
-      <c r="E39" s="49"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="51"/>
+      <c r="E39" s="44"/>
+      <c r="F39" s="45"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="46"/>
     </row>
     <row r="40" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A40" s="57"/>
+      <c r="A40" s="53"/>
       <c r="B40" s="10"/>
       <c r="C40" s="9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D40" s="20"/>
-      <c r="E40" s="49"/>
-      <c r="F40" s="50"/>
-      <c r="G40" s="50"/>
-      <c r="H40" s="51"/>
+      <c r="E40" s="44"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="45"/>
+      <c r="H40" s="46"/>
     </row>
     <row r="41" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A41" s="57"/>
+      <c r="A41" s="53"/>
       <c r="B41" s="10"/>
       <c r="C41" s="9" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D41" s="20"/>
-      <c r="E41" s="49"/>
-      <c r="F41" s="50"/>
-      <c r="G41" s="50"/>
-      <c r="H41" s="51"/>
+      <c r="E41" s="44"/>
+      <c r="F41" s="45"/>
+      <c r="G41" s="45"/>
+      <c r="H41" s="46"/>
     </row>
     <row r="42" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A42" s="57"/>
+      <c r="A42" s="53"/>
       <c r="B42" s="10"/>
       <c r="C42" s="9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D42" s="20"/>
-      <c r="E42" s="49"/>
-      <c r="F42" s="50"/>
-      <c r="G42" s="50"/>
-      <c r="H42" s="51"/>
+      <c r="E42" s="44"/>
+      <c r="F42" s="45"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="46"/>
     </row>
     <row r="43" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A43" s="57"/>
+      <c r="A43" s="53"/>
       <c r="B43" s="10"/>
       <c r="C43" s="9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D43" s="20"/>
-      <c r="E43" s="49"/>
-      <c r="F43" s="50"/>
-      <c r="G43" s="50"/>
-      <c r="H43" s="51"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="45"/>
+      <c r="G43" s="45"/>
+      <c r="H43" s="46"/>
     </row>
     <row r="44" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A44" s="57"/>
+      <c r="A44" s="53"/>
       <c r="B44" s="10"/>
       <c r="C44" s="9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D44" s="20"/>
-      <c r="E44" s="49"/>
-      <c r="F44" s="50"/>
-      <c r="G44" s="50"/>
-      <c r="H44" s="51"/>
+      <c r="E44" s="44"/>
+      <c r="F44" s="45"/>
+      <c r="G44" s="45"/>
+      <c r="H44" s="46"/>
     </row>
     <row r="45" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A45" s="57"/>
+      <c r="A45" s="53"/>
       <c r="B45" s="10"/>
       <c r="C45" s="9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D45" s="20"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="50"/>
-      <c r="G45" s="50"/>
-      <c r="H45" s="51"/>
+      <c r="E45" s="44"/>
+      <c r="F45" s="45"/>
+      <c r="G45" s="45"/>
+      <c r="H45" s="46"/>
     </row>
     <row r="46" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A46" s="57"/>
+      <c r="A46" s="53"/>
       <c r="B46" s="10"/>
       <c r="C46" s="9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D46" s="20"/>
-      <c r="E46" s="49"/>
-      <c r="F46" s="50"/>
-      <c r="G46" s="50"/>
-      <c r="H46" s="51"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="45"/>
+      <c r="G46" s="45"/>
+      <c r="H46" s="46"/>
     </row>
     <row r="47" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A47" s="57"/>
+      <c r="A47" s="53"/>
       <c r="B47" s="10"/>
       <c r="C47" s="9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D47" s="20"/>
-      <c r="E47" s="49"/>
-      <c r="F47" s="50"/>
-      <c r="G47" s="50"/>
-      <c r="H47" s="51"/>
+      <c r="E47" s="44"/>
+      <c r="F47" s="45"/>
+      <c r="G47" s="45"/>
+      <c r="H47" s="46"/>
     </row>
     <row r="48" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A48" s="57"/>
+      <c r="A48" s="53"/>
       <c r="B48" s="10"/>
       <c r="C48" s="9" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D48" s="20"/>
-      <c r="E48" s="49"/>
-      <c r="F48" s="50"/>
-      <c r="G48" s="50"/>
-      <c r="H48" s="51"/>
+      <c r="E48" s="44"/>
+      <c r="F48" s="45"/>
+      <c r="G48" s="45"/>
+      <c r="H48" s="46"/>
     </row>
     <row r="49" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A49" s="57"/>
+      <c r="A49" s="53"/>
       <c r="B49" s="10"/>
       <c r="C49" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D49" s="20"/>
-      <c r="E49" s="49"/>
-      <c r="F49" s="50"/>
-      <c r="G49" s="50"/>
-      <c r="H49" s="51"/>
+      <c r="E49" s="44"/>
+      <c r="F49" s="45"/>
+      <c r="G49" s="45"/>
+      <c r="H49" s="46"/>
     </row>
     <row r="50" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A50" s="57"/>
+      <c r="A50" s="53"/>
       <c r="B50" s="10"/>
       <c r="C50" s="9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D50" s="20"/>
-      <c r="E50" s="49"/>
-      <c r="F50" s="50"/>
-      <c r="G50" s="50"/>
-      <c r="H50" s="51"/>
+      <c r="E50" s="44"/>
+      <c r="F50" s="45"/>
+      <c r="G50" s="45"/>
+      <c r="H50" s="46"/>
     </row>
     <row r="51" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A51" s="57"/>
+      <c r="A51" s="53"/>
       <c r="B51" s="10"/>
       <c r="C51" s="9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D51" s="20"/>
-      <c r="E51" s="49"/>
-      <c r="F51" s="50"/>
-      <c r="G51" s="50"/>
-      <c r="H51" s="51"/>
+      <c r="E51" s="44"/>
+      <c r="F51" s="45"/>
+      <c r="G51" s="45"/>
+      <c r="H51" s="46"/>
     </row>
     <row r="52" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A52" s="57"/>
+      <c r="A52" s="53"/>
       <c r="B52" s="10"/>
       <c r="C52" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D52" s="20"/>
-      <c r="E52" s="49"/>
-      <c r="F52" s="50"/>
-      <c r="G52" s="50"/>
-      <c r="H52" s="51"/>
+      <c r="E52" s="44"/>
+      <c r="F52" s="45"/>
+      <c r="G52" s="45"/>
+      <c r="H52" s="46"/>
     </row>
     <row r="53" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A53" s="57"/>
+      <c r="A53" s="53"/>
       <c r="B53" s="10"/>
       <c r="C53" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D53" s="20"/>
-      <c r="E53" s="49"/>
-      <c r="F53" s="50"/>
-      <c r="G53" s="50"/>
-      <c r="H53" s="51"/>
+      <c r="E53" s="44"/>
+      <c r="F53" s="45"/>
+      <c r="G53" s="45"/>
+      <c r="H53" s="46"/>
     </row>
     <row r="54" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A54" s="58"/>
+      <c r="A54" s="54"/>
       <c r="B54" s="10"/>
       <c r="D54" s="20"/>
-      <c r="E54" s="49"/>
-      <c r="F54" s="50"/>
-      <c r="G54" s="50"/>
-      <c r="H54" s="51"/>
+      <c r="E54" s="44"/>
+      <c r="F54" s="45"/>
+      <c r="G54" s="45"/>
+      <c r="H54" s="46"/>
     </row>
     <row r="55" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A55" s="59" t="s">
-        <v>15</v>
+      <c r="A55" s="55" t="s">
+        <v>12</v>
       </c>
       <c r="B55" s="10"/>
       <c r="C55" s="9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D55" s="20"/>
-      <c r="E55" s="49"/>
-      <c r="F55" s="50"/>
-      <c r="G55" s="50"/>
-      <c r="H55" s="51"/>
+      <c r="E55" s="44"/>
+      <c r="F55" s="45"/>
+      <c r="G55" s="45"/>
+      <c r="H55" s="46"/>
     </row>
     <row r="56" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A56" s="59"/>
+      <c r="A56" s="55"/>
       <c r="B56" s="8"/>
       <c r="C56" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D56" s="21"/>
-      <c r="E56" s="49"/>
-      <c r="F56" s="50"/>
-      <c r="G56" s="50"/>
-      <c r="H56" s="51"/>
+      <c r="E56" s="44"/>
+      <c r="F56" s="45"/>
+      <c r="G56" s="45"/>
+      <c r="H56" s="46"/>
     </row>
     <row r="57" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A57" s="59"/>
+      <c r="A57" s="55"/>
       <c r="B57" s="8"/>
       <c r="C57" s="9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D57" s="21"/>
-      <c r="E57" s="49"/>
-      <c r="F57" s="50"/>
-      <c r="G57" s="50"/>
-      <c r="H57" s="51"/>
+      <c r="E57" s="44"/>
+      <c r="F57" s="45"/>
+      <c r="G57" s="45"/>
+      <c r="H57" s="46"/>
     </row>
     <row r="58" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A58" s="59"/>
+      <c r="A58" s="55"/>
       <c r="B58" s="8"/>
       <c r="C58" s="9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D58" s="21"/>
-      <c r="E58" s="49"/>
-      <c r="F58" s="50"/>
-      <c r="G58" s="50"/>
-      <c r="H58" s="51"/>
+      <c r="E58" s="44"/>
+      <c r="F58" s="45"/>
+      <c r="G58" s="45"/>
+      <c r="H58" s="46"/>
     </row>
     <row r="59" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A59" s="59"/>
+      <c r="A59" s="55"/>
       <c r="B59" s="8"/>
       <c r="D59" s="21"/>
-      <c r="E59" s="50"/>
-      <c r="F59" s="50"/>
-      <c r="G59" s="50"/>
-      <c r="H59" s="51"/>
+      <c r="E59" s="45"/>
+      <c r="F59" s="45"/>
+      <c r="G59" s="45"/>
+      <c r="H59" s="46"/>
     </row>
     <row r="60" spans="1:8" s="6" customFormat="1" ht="9" customHeight="1">
-      <c r="A60" s="60"/>
+      <c r="A60" s="56"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
       <c r="D60" s="22"/>
-      <c r="E60" s="50"/>
-      <c r="F60" s="50"/>
-      <c r="G60" s="50"/>
-      <c r="H60" s="51"/>
+      <c r="E60" s="45"/>
+      <c r="F60" s="45"/>
+      <c r="G60" s="45"/>
+      <c r="H60" s="46"/>
     </row>
     <row r="61" spans="1:8" ht="9" customHeight="1">
-      <c r="A61" s="60"/>
+      <c r="A61" s="56"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="22"/>
-      <c r="E61" s="50"/>
-      <c r="F61" s="50"/>
-      <c r="G61" s="50"/>
-      <c r="H61" s="51"/>
+      <c r="E61" s="45"/>
+      <c r="F61" s="45"/>
+      <c r="G61" s="45"/>
+      <c r="H61" s="46"/>
     </row>
     <row r="62" spans="1:8" ht="9" customHeight="1">
-      <c r="A62" s="60"/>
+      <c r="A62" s="56"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
       <c r="D62" s="22"/>
-      <c r="E62" s="50"/>
-      <c r="F62" s="50"/>
-      <c r="G62" s="50"/>
-      <c r="H62" s="51"/>
+      <c r="E62" s="45"/>
+      <c r="F62" s="45"/>
+      <c r="G62" s="45"/>
+      <c r="H62" s="46"/>
     </row>
     <row r="63" spans="1:8" ht="9" customHeight="1">
-      <c r="A63" s="60"/>
+      <c r="A63" s="56"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
       <c r="D63" s="23"/>
-      <c r="E63" s="50"/>
-      <c r="F63" s="50"/>
-      <c r="G63" s="50"/>
-      <c r="H63" s="51"/>
+      <c r="E63" s="45"/>
+      <c r="F63" s="45"/>
+      <c r="G63" s="45"/>
+      <c r="H63" s="46"/>
     </row>
     <row r="64" spans="1:8" ht="9" customHeight="1">
-      <c r="A64" s="60"/>
+      <c r="A64" s="56"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
       <c r="D64" s="23"/>
-      <c r="E64" s="50"/>
-      <c r="F64" s="50"/>
-      <c r="G64" s="50"/>
-      <c r="H64" s="51"/>
+      <c r="E64" s="45"/>
+      <c r="F64" s="45"/>
+      <c r="G64" s="45"/>
+      <c r="H64" s="46"/>
     </row>
     <row r="65" spans="1:8" ht="9" customHeight="1">
-      <c r="A65" s="60"/>
+      <c r="A65" s="56"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
       <c r="D65" s="23"/>
-      <c r="E65" s="50"/>
-      <c r="F65" s="50"/>
-      <c r="G65" s="50"/>
-      <c r="H65" s="51"/>
+      <c r="E65" s="45"/>
+      <c r="F65" s="45"/>
+      <c r="G65" s="45"/>
+      <c r="H65" s="46"/>
     </row>
     <row r="66" spans="1:8" ht="9" customHeight="1">
-      <c r="A66" s="61"/>
+      <c r="A66" s="57"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
       <c r="D66" s="23"/>
-      <c r="E66" s="50"/>
-      <c r="F66" s="50"/>
-      <c r="G66" s="50"/>
-      <c r="H66" s="51"/>
+      <c r="E66" s="45"/>
+      <c r="F66" s="45"/>
+      <c r="G66" s="45"/>
+      <c r="H66" s="46"/>
     </row>
     <row r="67" spans="1:8" ht="9" customHeight="1">
       <c r="A67" s="34" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B67" s="35"/>
       <c r="C67" s="35"/>
-      <c r="D67" s="63" t="s">
-        <v>9</v>
-      </c>
-      <c r="E67" s="63"/>
-      <c r="F67" s="63"/>
-      <c r="G67" s="63"/>
-      <c r="H67" s="64"/>
+      <c r="D67" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="E67" s="58"/>
+      <c r="F67" s="58"/>
+      <c r="G67" s="58"/>
+      <c r="H67" s="59"/>
     </row>
     <row r="68" spans="1:8" ht="9" customHeight="1">
       <c r="A68" s="34"/>
       <c r="B68" s="35"/>
       <c r="C68" s="35"/>
-      <c r="D68" s="76" t="s">
-        <v>82</v>
-      </c>
-      <c r="E68" s="76"/>
-      <c r="F68" s="76" t="s">
-        <v>8</v>
-      </c>
-      <c r="G68" s="76"/>
+      <c r="D68" s="71" t="s">
+        <v>79</v>
+      </c>
+      <c r="E68" s="71"/>
+      <c r="F68" s="71" t="s">
+        <v>5</v>
+      </c>
+      <c r="G68" s="71"/>
       <c r="H68" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="9" customHeight="1">
       <c r="A69" s="34"/>
       <c r="B69" s="35"/>
       <c r="C69" s="35"/>
-      <c r="D69" s="77"/>
-      <c r="E69" s="77"/>
-      <c r="F69" s="76"/>
-      <c r="G69" s="76"/>
+      <c r="D69" s="72"/>
+      <c r="E69" s="72"/>
+      <c r="F69" s="71"/>
+      <c r="G69" s="71"/>
       <c r="H69" s="2"/>
     </row>
     <row r="70" spans="1:8" ht="9" customHeight="1">
       <c r="A70" s="34"/>
       <c r="B70" s="35"/>
       <c r="C70" s="35"/>
-      <c r="D70" s="77"/>
-      <c r="E70" s="77"/>
-      <c r="F70" s="76"/>
-      <c r="G70" s="76"/>
+      <c r="D70" s="72"/>
+      <c r="E70" s="72"/>
+      <c r="F70" s="71"/>
+      <c r="G70" s="71"/>
       <c r="H70" s="2"/>
     </row>
     <row r="71" spans="1:8" ht="9" customHeight="1">
       <c r="A71" s="34"/>
       <c r="B71" s="35"/>
       <c r="C71" s="35"/>
-      <c r="D71" s="77"/>
-      <c r="E71" s="77"/>
-      <c r="F71" s="76"/>
-      <c r="G71" s="76"/>
+      <c r="D71" s="72"/>
+      <c r="E71" s="72"/>
+      <c r="F71" s="71"/>
+      <c r="G71" s="71"/>
       <c r="H71" s="2"/>
     </row>
     <row r="72" spans="1:8" ht="9" customHeight="1">
       <c r="A72" s="34"/>
       <c r="B72" s="35"/>
       <c r="C72" s="35"/>
-      <c r="D72" s="77"/>
-      <c r="E72" s="77"/>
-      <c r="F72" s="76"/>
-      <c r="G72" s="76"/>
+      <c r="D72" s="72"/>
+      <c r="E72" s="72"/>
+      <c r="F72" s="71"/>
+      <c r="G72" s="71"/>
       <c r="H72" s="2"/>
     </row>
     <row r="73" spans="1:8" ht="9" customHeight="1">
       <c r="A73" s="34"/>
       <c r="B73" s="35"/>
       <c r="C73" s="35"/>
-      <c r="D73" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="E73" s="47"/>
-      <c r="F73" s="48"/>
+      <c r="D73" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="E73" s="42"/>
+      <c r="F73" s="43"/>
       <c r="G73" s="28"/>
       <c r="H73" s="29"/>
     </row>
@@ -2269,7 +2241,7 @@
       <c r="B74" s="35"/>
       <c r="C74" s="35"/>
       <c r="D74" s="38" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E74" s="39"/>
       <c r="F74" s="40"/>
@@ -2280,11 +2252,11 @@
       <c r="A75" s="34"/>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
-      <c r="D75" s="62" t="s">
-        <v>4</v>
-      </c>
-      <c r="E75" s="41"/>
-      <c r="F75" s="42"/>
+      <c r="D75" s="73" t="s">
+        <v>82</v>
+      </c>
+      <c r="E75" s="73"/>
+      <c r="F75" s="73"/>
       <c r="G75" s="28"/>
       <c r="H75" s="29"/>
     </row>
@@ -2293,7 +2265,7 @@
       <c r="B76" s="35"/>
       <c r="C76" s="35"/>
       <c r="D76" s="38" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E76" s="39"/>
       <c r="F76" s="40"/>
@@ -2304,11 +2276,11 @@
       <c r="A77" s="34"/>
       <c r="B77" s="35"/>
       <c r="C77" s="35"/>
-      <c r="D77" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="E77" s="41"/>
-      <c r="F77" s="42"/>
+      <c r="D77" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="E77" s="47"/>
+      <c r="F77" s="47"/>
       <c r="G77" s="28"/>
       <c r="H77" s="29"/>
     </row>
@@ -2316,20 +2288,20 @@
       <c r="A78" s="36"/>
       <c r="B78" s="37"/>
       <c r="C78" s="37"/>
-      <c r="D78" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="E78" s="44"/>
-      <c r="F78" s="45"/>
+      <c r="D78" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="E78" s="39"/>
+      <c r="F78" s="40"/>
       <c r="G78" s="32"/>
       <c r="H78" s="33"/>
     </row>
     <row r="79" spans="1:8" ht="9" customHeight="1" thickTop="1">
-      <c r="F79" s="52" t="s">
+      <c r="F79" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="G79" s="52"/>
-      <c r="H79" s="52"/>
+      <c r="G79" s="48"/>
+      <c r="H79" s="48"/>
     </row>
     <row r="80" spans="1:8" ht="9" customHeight="1">
       <c r="A80"/>
@@ -2350,6 +2322,7 @@
     <row r="87" customFormat="1"/>
   </sheetData>
   <mergeCells count="101">
+    <mergeCell ref="D75:F75"/>
     <mergeCell ref="D68:E68"/>
     <mergeCell ref="D69:E69"/>
     <mergeCell ref="D70:E70"/>
@@ -2390,6 +2363,9 @@
     <mergeCell ref="E18:H18"/>
     <mergeCell ref="E19:H19"/>
     <mergeCell ref="E20:H20"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
     <mergeCell ref="E31:H31"/>
     <mergeCell ref="E32:H32"/>
     <mergeCell ref="E33:H33"/>
@@ -2400,16 +2376,16 @@
     <mergeCell ref="E28:H28"/>
     <mergeCell ref="E29:H29"/>
     <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A23"/>
+    <mergeCell ref="A24:A32"/>
+    <mergeCell ref="A33:A37"/>
+    <mergeCell ref="A38:A54"/>
+    <mergeCell ref="A55:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="D67:H67"/>
     <mergeCell ref="E62:H62"/>
     <mergeCell ref="E63:H63"/>
     <mergeCell ref="E64:H64"/>
@@ -2423,26 +2399,12 @@
     <mergeCell ref="E52:H52"/>
     <mergeCell ref="E53:H53"/>
     <mergeCell ref="E54:H54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A23"/>
-    <mergeCell ref="A24:A32"/>
-    <mergeCell ref="A33:A37"/>
-    <mergeCell ref="A38:A54"/>
-    <mergeCell ref="A55:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="D67:H67"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="G73:H74"/>
     <mergeCell ref="G75:H76"/>
     <mergeCell ref="G77:H78"/>
     <mergeCell ref="A67:C78"/>
     <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D78:F78"/>
     <mergeCell ref="D73:F73"/>
     <mergeCell ref="D74:F74"/>
     <mergeCell ref="E56:H56"/>
@@ -2451,6 +2413,16 @@
     <mergeCell ref="E59:H59"/>
     <mergeCell ref="E60:H60"/>
     <mergeCell ref="E61:H61"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="E37:H37"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.195138888888889" bottom="0" header="0" footer="0"/>
